--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E61E8187-B145-42FF-9104-0935B6C5CD9C}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF456451-B47F-4768-AEFA-9B4D323BCE8F}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" tabRatio="819" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
     <sheet name="equipo" sheetId="2" r:id="rId2"/>
-    <sheet name="productos criticos" sheetId="3" r:id="rId3"/>
-    <sheet name="datos_ops" sheetId="4" r:id="rId4"/>
-    <sheet name="resultados" sheetId="5" r:id="rId5"/>
+    <sheet name="datos_ops" sheetId="4" r:id="rId3"/>
+    <sheet name="resultados" sheetId="5" r:id="rId4"/>
+    <sheet name="productos criticos" sheetId="3" r:id="rId5"/>
     <sheet name="productos_resultados" sheetId="6" r:id="rId6"/>
     <sheet name="productos_adquisiciones" sheetId="7" r:id="rId7"/>
     <sheet name="comentarios_clausulas" sheetId="8" r:id="rId8"/>
@@ -25,9 +25,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'productos criticos'!$B$3:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$F$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">productos_resultados!$A$3:$C$182</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">resultados!$A$3:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">resultados!$A$3:$H$113</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -3018,17 +3018,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D78"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="8" customWidth="1"/>
     <col min="3" max="3" width="42" style="8" customWidth="1"/>
     <col min="4" max="4" width="80" style="8" customWidth="1"/>
-    <col min="5" max="15" width="8.88671875" style="8" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="8"/>
+    <col min="5" max="15" width="8.85546875" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>122</v>
       </c>
@@ -3036,8 +3036,8 @@
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>131</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>29</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>24</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>64</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>6</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>131</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>29</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>33</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>64</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>6</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>131</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>29</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>33</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>24</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>64</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>14</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>6</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>131</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>29</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>33</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>21</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>14</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>6</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>6</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>18</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>131</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>29</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>33</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>24</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>64</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>14</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>6</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>131</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>29</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>33</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>14</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>6</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>18</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>131</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>29</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>33</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>24</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>64</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>6</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>18</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>29</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>33</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>14</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>64</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>6</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>6</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>85</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>85</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>85</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>85</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>14</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>33</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>6</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>64</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>18</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>29</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>14</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>24</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>18</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>33</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>6</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>64</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>85</v>
       </c>
@@ -4113,32 +4113,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="5">
         <v>46261</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>287</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>288</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>296</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>296</v>
       </c>
@@ -4264,7 +4264,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>303</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>308</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>310</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>312</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>314</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>317</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>317</v>
       </c>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>323</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>330</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>332</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>336</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>341</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>343</v>
       </c>
@@ -4648,10 +4648,10 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C23" s="4"/>
     </row>
   </sheetData>
@@ -4660,1153 +4660,206 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:F71"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B1:E13"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="12" style="18" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="18" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="98.109375" style="18" customWidth="1"/>
-    <col min="7" max="18" width="8.88671875" style="18" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="18"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+    <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>456</v>
+      </c>
+      <c r="D4" t="s">
+        <v>457</v>
+      </c>
+      <c r="E4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>459</v>
+      </c>
+      <c r="D5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D6" t="s">
+        <v>463</v>
+      </c>
+      <c r="E6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="C7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D7" t="s">
+        <v>466</v>
+      </c>
+      <c r="E7" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>377</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-    </row>
-    <row r="19" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-    </row>
-    <row r="24" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-    </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>388</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-    </row>
-    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>389</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-    </row>
-    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E28" s="20"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E29" s="20"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E30" s="20"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E31" s="20"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E32" s="20"/>
-    </row>
-    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>397</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="F35" s="23"/>
-    </row>
-    <row r="36" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>406</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E37" s="21"/>
-      <c r="F37" s="15"/>
-    </row>
-    <row r="38" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>407</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="15"/>
-    </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-    </row>
-    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="18" t="s">
+      <c r="C8" t="s">
+        <v>468</v>
+      </c>
+      <c r="D8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" t="s">
+        <v>471</v>
+      </c>
+      <c r="D9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" t="s">
+        <v>475</v>
+      </c>
+      <c r="E10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>477</v>
+      </c>
+      <c r="D11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E11" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D12" t="s">
+        <v>481</v>
+      </c>
+      <c r="E12" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-    </row>
-    <row r="50" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>426</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-    </row>
-    <row r="51" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>427</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-    </row>
-    <row r="52" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>428</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-    </row>
-    <row r="53" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>429</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-    </row>
-    <row r="54" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-    </row>
-    <row r="55" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-    </row>
-    <row r="56" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>432</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-    </row>
-    <row r="57" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>433</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-    </row>
-    <row r="58" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>434</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-    </row>
-    <row r="59" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>435</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-    </row>
-    <row r="60" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-    </row>
-    <row r="61" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>437</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-    </row>
-    <row r="62" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>438</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-    </row>
-    <row r="63" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="22" t="s">
-        <v>439</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-    </row>
-    <row r="64" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="22" t="s">
-        <v>440</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-    </row>
-    <row r="65" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>441</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-    </row>
-    <row r="66" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>442</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-    </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="22" t="s">
-        <v>443</v>
-      </c>
-      <c r="D67" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-    </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>444</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-    </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>445</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-    </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>446</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-    </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>447</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
+      <c r="C13" t="s">
+        <v>483</v>
+      </c>
+      <c r="D13" t="s">
+        <v>484</v>
+      </c>
+      <c r="E13" t="s">
+        <v>485</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:F34" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
-    <col min="5" max="5" width="44.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D3" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>456</v>
-      </c>
-      <c r="D4" t="s">
-        <v>457</v>
-      </c>
-      <c r="E4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>459</v>
-      </c>
-      <c r="D5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>462</v>
-      </c>
-      <c r="D6" t="s">
-        <v>463</v>
-      </c>
-      <c r="E6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>465</v>
-      </c>
-      <c r="D7" t="s">
-        <v>466</v>
-      </c>
-      <c r="E7" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>468</v>
-      </c>
-      <c r="D8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" t="s">
-        <v>471</v>
-      </c>
-      <c r="D9" t="s">
-        <v>472</v>
-      </c>
-      <c r="E9" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>474</v>
-      </c>
-      <c r="D10" t="s">
-        <v>475</v>
-      </c>
-      <c r="E10" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>477</v>
-      </c>
-      <c r="D11" t="s">
-        <v>478</v>
-      </c>
-      <c r="E11" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>480</v>
-      </c>
-      <c r="D12" t="s">
-        <v>481</v>
-      </c>
-      <c r="E12" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>483</v>
-      </c>
-      <c r="D13" t="s">
-        <v>484</v>
-      </c>
-      <c r="E13" t="s">
-        <v>485</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -5817,7 +4870,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>486</v>
       </c>
@@ -5829,8 +4882,8 @@
       <c r="G1" s="27"/>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -5856,7 +4909,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5882,7 +4935,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5908,7 +4961,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -5934,7 +4987,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -5960,7 +5013,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5986,7 +5039,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -6012,7 +5065,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -6038,7 +5091,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -6064,7 +5117,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -6090,7 +5143,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -6116,7 +5169,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -6142,7 +5195,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6168,7 +5221,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -6194,7 +5247,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -6220,7 +5273,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -6246,7 +5299,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -6272,7 +5325,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -6298,7 +5351,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -6324,7 +5377,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -6350,7 +5403,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -6376,7 +5429,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -6402,7 +5455,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -6428,7 +5481,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -6454,7 +5507,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -6480,7 +5533,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -6506,7 +5559,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -6532,7 +5585,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -6558,7 +5611,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -6584,7 +5637,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -6610,7 +5663,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -6636,7 +5689,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -6662,7 +5715,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -6688,7 +5741,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -6714,7 +5767,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -6740,7 +5793,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -6766,7 +5819,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -6792,7 +5845,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -6818,7 +5871,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -6844,7 +5897,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -6870,7 +5923,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -6896,7 +5949,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -6922,7 +5975,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -6948,7 +6001,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -6974,7 +6027,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -7000,7 +6053,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -7026,7 +6079,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -7052,7 +6105,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -7078,7 +6131,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -7104,7 +6157,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -7130,7 +6183,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -7156,7 +6209,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -7182,7 +6235,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -7208,7 +6261,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -7234,7 +6287,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -7260,7 +6313,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7286,7 +6339,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7312,7 +6365,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7338,7 +6391,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7364,7 +6417,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7390,7 +6443,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>29</v>
       </c>
@@ -7416,7 +6469,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>29</v>
       </c>
@@ -7442,7 +6495,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -7468,7 +6521,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>29</v>
       </c>
@@ -7494,7 +6547,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -7520,7 +6573,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -7546,7 +6599,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -7572,7 +6625,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -7598,7 +6651,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -7624,7 +6677,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -7650,7 +6703,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -7676,7 +6729,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -7702,7 +6755,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -7728,7 +6781,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -7754,7 +6807,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -7780,7 +6833,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -7806,7 +6859,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>70</v>
       </c>
@@ -7832,7 +6885,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -7858,7 +6911,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>70</v>
       </c>
@@ -7884,7 +6937,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -7910,7 +6963,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>70</v>
       </c>
@@ -7936,7 +6989,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>70</v>
       </c>
@@ -7962,7 +7015,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>70</v>
       </c>
@@ -7988,7 +7041,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>70</v>
       </c>
@@ -8014,7 +7067,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>70</v>
       </c>
@@ -8040,7 +7093,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>70</v>
       </c>
@@ -8066,7 +7119,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>70</v>
       </c>
@@ -8092,7 +7145,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>70</v>
       </c>
@@ -8118,7 +7171,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>70</v>
       </c>
@@ -8144,7 +7197,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>70</v>
       </c>
@@ -8170,7 +7223,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>64</v>
       </c>
@@ -8196,7 +7249,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>64</v>
       </c>
@@ -8222,7 +7275,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>64</v>
       </c>
@@ -8248,7 +7301,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>64</v>
       </c>
@@ -8274,7 +7327,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>64</v>
       </c>
@@ -8300,7 +7353,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>64</v>
       </c>
@@ -8326,7 +7379,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>64</v>
       </c>
@@ -8352,7 +7405,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>64</v>
       </c>
@@ -8378,7 +7431,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -8404,7 +7457,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -8430,7 +7483,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -8456,7 +7509,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>33</v>
       </c>
@@ -8482,7 +7535,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -8508,7 +7561,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -8534,7 +7587,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -8560,12 +7613,12 @@
         <v>507</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:H113" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
@@ -8575,24 +7628,971 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B2:F71"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="12" style="18" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" style="18" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="98.140625" style="18" customWidth="1"/>
+    <col min="7" max="18" width="8.85546875" style="18" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+    </row>
+    <row r="19" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+    </row>
+    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E28" s="20"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E32" s="20"/>
+    </row>
+    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="F35" s="23"/>
+    </row>
+    <row r="36" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+    </row>
+    <row r="50" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+    </row>
+    <row r="51" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>427</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+    </row>
+    <row r="52" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+    </row>
+    <row r="53" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+    </row>
+    <row r="54" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+    </row>
+    <row r="55" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+    </row>
+    <row r="56" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+    </row>
+    <row r="57" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+    </row>
+    <row r="58" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+    </row>
+    <row r="59" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+    </row>
+    <row r="60" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+    </row>
+    <row r="61" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+    </row>
+    <row r="62" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+    </row>
+    <row r="63" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+    </row>
+    <row r="64" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+    </row>
+    <row r="65" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+    </row>
+    <row r="66" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+    </row>
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+    </row>
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+    </row>
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+    </row>
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+    </row>
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B3:F34" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>695</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
     </row>
-    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -8669,7 +8669,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8680,7 +8680,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -8812,7 +8812,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -8944,7 +8944,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -9175,7 +9175,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -9252,7 +9252,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -9274,7 +9274,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>29</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>29</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>29</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -9450,7 +9450,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>29</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>29</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -9527,7 +9527,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>29</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>29</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>29</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>21</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>21</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>21</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>21</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>21</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>21</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>21</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>21</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>21</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>70</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>70</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>70</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>70</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>70</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>70</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>70</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>70</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>70</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>70</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>70</v>
       </c>
@@ -9857,7 +9857,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>70</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>70</v>
       </c>
@@ -9879,7 +9879,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>70</v>
       </c>
@@ -9890,7 +9890,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>70</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>70</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>70</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>70</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>70</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>70</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>70</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>64</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>64</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>64</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>64</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>64</v>
       </c>
@@ -10033,7 +10033,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>64</v>
       </c>
@@ -10044,7 +10044,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>64</v>
       </c>
@@ -10055,7 +10055,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>64</v>
       </c>
@@ -10066,7 +10066,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>64</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>64</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>64</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>64</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>64</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>64</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>64</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>64</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>64</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>64</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>64</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>64</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>64</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>64</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>64</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>64</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>64</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>64</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>64</v>
       </c>
@@ -10275,7 +10275,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>64</v>
       </c>
@@ -10286,7 +10286,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>64</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>64</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>64</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>33</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>33</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>33</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>33</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>33</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>33</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>33</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>33</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>33</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>33</v>
       </c>
@@ -10440,7 +10440,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>33</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>33</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>33</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>33</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -10495,13 +10495,13 @@
         <v>408</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:C182" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="1">
@@ -10514,7 +10514,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10523,7 +10523,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>702</v>
       </c>
@@ -10532,7 +10532,7 @@
       <c r="D1" s="27"/>
       <c r="E1" s="27"/>
     </row>
-    <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>345</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -10847,7 +10847,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>33</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>33</v>
       </c>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="E33" s="15"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>33</v>
       </c>
@@ -11014,7 +11014,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>33</v>
       </c>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="E35" s="15"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -11190,7 +11190,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -11207,7 +11207,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -11221,7 +11221,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -11272,7 +11272,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -11300,7 +11300,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -11393,7 +11393,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -11435,7 +11435,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -11463,7 +11463,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -11477,7 +11477,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -11502,7 +11502,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -11511,7 +11511,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>780</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>786</v>
       </c>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>790</v>
       </c>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>792</v>
       </c>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>794</v>
       </c>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>692694</v>
       </c>
@@ -11633,16 +11633,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A2:E89"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>4</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>4</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>4</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>4</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>4</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>4</v>
       </c>
@@ -11838,7 +11838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>4</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>4</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="7">
         <v>46092</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="7">
         <v>46092</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="7">
         <v>46092</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="7">
         <v>46092</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="7">
         <v>46092</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="7">
         <v>46092</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="7">
         <v>46092</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="7">
         <v>46119</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="7">
         <v>46119</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7">
         <v>46119</v>
       </c>
@@ -12020,7 +12020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="7">
         <v>46119</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="7">
         <v>46121</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="7">
         <v>46121</v>
       </c>
@@ -12062,7 +12062,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="7">
         <v>46126</v>
       </c>
@@ -12076,7 +12076,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="7">
         <v>46134</v>
       </c>
@@ -12090,7 +12090,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="7">
         <v>46134</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="7">
         <v>46142</v>
       </c>
@@ -12118,7 +12118,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="7">
         <v>46160</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="7">
         <v>46169</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="7">
         <v>46170</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
         <v>46170</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="7">
         <v>46170</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="7">
         <v>46171</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="7">
         <v>46171</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="7">
         <v>46171</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="7">
         <v>46171</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="7">
         <v>46171</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="7">
         <v>46175</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="7">
         <v>46175</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="7">
         <v>46175</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="7">
         <v>46175</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="7">
         <v>46175</v>
       </c>
@@ -12328,7 +12328,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="7">
         <v>46175</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
         <v>46178</v>
       </c>
@@ -12356,7 +12356,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="7">
         <v>46178</v>
       </c>
@@ -12370,7 +12370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="7">
         <v>46178</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="7">
         <v>46178</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="7">
         <v>46178</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="7">
         <v>46184</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="7">
         <v>46188</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="7">
         <v>46189</v>
       </c>
@@ -12454,7 +12454,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="7">
         <v>46189</v>
       </c>
@@ -12468,7 +12468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="7">
         <v>46211</v>
       </c>
@@ -12482,7 +12482,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" s="7">
         <v>46212</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" s="7">
         <v>46212</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" s="7">
         <v>46212</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B65" s="7">
         <v>46212</v>
       </c>
@@ -12538,7 +12538,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B66" s="7">
         <v>46212</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B67" s="7">
         <v>46212</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B68" s="7">
         <v>46212</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B69" s="7">
         <v>46212</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B70" s="7">
         <v>46212</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B71" s="7">
         <v>46216</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B72" s="7">
         <v>46216</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B73" s="7">
         <v>46216</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B74" s="7">
         <v>46225</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B75" s="7">
         <v>46240</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B76" s="7">
         <v>46240</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B77" s="7">
         <v>46245</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B78" s="7">
         <v>46246</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="16">
         <v>46247</v>
@@ -12735,7 +12735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B80" s="16">
         <v>46251</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B81" s="16">
         <v>46253</v>
       </c>
@@ -12763,7 +12763,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B82" s="16">
         <v>46253</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" s="16">
         <v>46253</v>
       </c>
@@ -12791,7 +12791,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B84" s="16">
         <v>46253</v>
       </c>
@@ -12805,7 +12805,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B85" s="16">
         <v>46253</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B86" s="16">
         <v>46253</v>
       </c>
@@ -12833,7 +12833,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" s="16">
         <v>46253</v>
       </c>
@@ -12847,7 +12847,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B88" s="16">
         <v>46253</v>
       </c>
@@ -12861,7 +12861,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" s="16">
         <v>46253</v>
       </c>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF456451-B47F-4768-AEFA-9B4D323BCE8F}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A199D54-0434-4DE9-8C6B-9520FBDE4A17}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="2760" windowWidth="26040" windowHeight="11175" tabRatio="819" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="808">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2444,6 +2444,21 @@
   </si>
   <si>
     <t>UGALDE VARGAS, DAYANA</t>
+  </si>
+  <si>
+    <t>Informe recibido 31/agosto/. En Revisión.</t>
+  </si>
+  <si>
+    <t>Informe recibido 5/agosto/. En Revisión.</t>
+  </si>
+  <si>
+    <t>Informe recibido 12/agosto/. En Revisión.</t>
+  </si>
+  <si>
+    <t>Resuelto</t>
+  </si>
+  <si>
+    <t>Informe recibido 28/agosto/. En Revisión.</t>
   </si>
 </sst>
 </file>
@@ -11501,7 +11516,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -11545,7 +11560,7 @@
         <v>788</v>
       </c>
       <c r="E2" t="s">
-        <v>789</v>
+        <v>806</v>
       </c>
       <c r="F2" s="12"/>
     </row>
@@ -11617,6 +11632,108 @@
         <v>795</v>
       </c>
       <c r="E6" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>708274</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D7" t="s">
+        <v>805</v>
+      </c>
+      <c r="E7" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <v>691920</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C8" t="s">
+        <v>787</v>
+      </c>
+      <c r="D8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E8" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <v>691923</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C9" t="s">
+        <v>787</v>
+      </c>
+      <c r="D9" t="s">
+        <v>804</v>
+      </c>
+      <c r="E9" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>701797</v>
+      </c>
+      <c r="B10" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C10" t="s">
+        <v>787</v>
+      </c>
+      <c r="D10" t="s">
+        <v>805</v>
+      </c>
+      <c r="E10" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>701540</v>
+      </c>
+      <c r="B11" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C11" t="s">
+        <v>787</v>
+      </c>
+      <c r="D11" t="s">
+        <v>803</v>
+      </c>
+      <c r="E11" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>692683</v>
+      </c>
+      <c r="B12" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C12" t="s">
+        <v>787</v>
+      </c>
+      <c r="D12" t="s">
+        <v>807</v>
+      </c>
+      <c r="E12" t="s">
         <v>789</v>
       </c>
     </row>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A199D54-0434-4DE9-8C6B-9520FBDE4A17}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58561800-C70F-4911-99FB-F0513FB7635C}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="2760" windowWidth="26040" windowHeight="11175" tabRatio="819" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45885" yWindow="2490" windowWidth="27450" windowHeight="15285" tabRatio="819" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="809">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2299,18 +2299,6 @@
     <t>CR-L1137-P00198</t>
   </si>
   <si>
-    <t>CR-L1137-P00326</t>
-  </si>
-  <si>
-    <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
-  </si>
-  <si>
-    <t>CR-L1137-P00327</t>
-  </si>
-  <si>
-    <t>CR-L1137-P00347</t>
-  </si>
-  <si>
     <t>CR-L1137-P00314</t>
   </si>
   <si>
@@ -2459,6 +2447,21 @@
   </si>
   <si>
     <t>Informe recibido 28/agosto/. En Revisión.</t>
+  </si>
+  <si>
+    <t>CR-L1137-P00404</t>
+  </si>
+  <si>
+    <t>CR-L1137-P00406</t>
+  </si>
+  <si>
+    <t>CR-L1137-P00405</t>
+  </si>
+  <si>
+    <t>Proceso estimados para finalizar luego del fin del plazo de desembolsos. Corresponden a contratos de finalización de obras de otro contrato cancelado anticipadamente.</t>
+  </si>
+  <si>
+    <t>Modelo desarrollado. Implementación requiere finalización de CCP que están en proceso de licitación.</t>
   </si>
 </sst>
 </file>
@@ -3033,17 +3036,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D78"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="8" customWidth="1"/>
     <col min="3" max="3" width="42" style="8" customWidth="1"/>
     <col min="4" max="4" width="80" style="8" customWidth="1"/>
-    <col min="5" max="15" width="8.85546875" style="8" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="8"/>
+    <col min="5" max="15" width="8.88671875" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>122</v>
       </c>
@@ -3051,8 +3054,8 @@
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -3066,7 +3069,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
@@ -3080,7 +3083,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
@@ -3094,7 +3097,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>131</v>
       </c>
@@ -3108,7 +3111,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>29</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -3136,7 +3139,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>24</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>64</v>
       </c>
@@ -3164,7 +3167,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>6</v>
       </c>
@@ -3178,7 +3181,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>131</v>
       </c>
@@ -3192,7 +3195,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>29</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>33</v>
       </c>
@@ -3220,7 +3223,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
@@ -3234,7 +3237,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>64</v>
       </c>
@@ -3248,7 +3251,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
@@ -3262,7 +3265,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>6</v>
       </c>
@@ -3276,7 +3279,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
@@ -3290,7 +3293,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>131</v>
       </c>
@@ -3304,7 +3307,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>29</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>33</v>
       </c>
@@ -3332,7 +3335,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>24</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>64</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>14</v>
       </c>
@@ -3374,7 +3377,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>6</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>131</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>29</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>33</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
@@ -3444,7 +3447,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>21</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>14</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>6</v>
       </c>
@@ -3486,7 +3489,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>6</v>
       </c>
@@ -3500,7 +3503,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>18</v>
       </c>
@@ -3514,7 +3517,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>131</v>
       </c>
@@ -3528,7 +3531,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>29</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>33</v>
       </c>
@@ -3556,7 +3559,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>24</v>
       </c>
@@ -3570,7 +3573,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>64</v>
       </c>
@@ -3584,7 +3587,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>14</v>
       </c>
@@ -3598,7 +3601,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>6</v>
       </c>
@@ -3612,7 +3615,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>131</v>
       </c>
@@ -3626,7 +3629,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>29</v>
       </c>
@@ -3640,7 +3643,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>33</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>14</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>6</v>
       </c>
@@ -3682,7 +3685,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>18</v>
       </c>
@@ -3696,7 +3699,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>131</v>
       </c>
@@ -3710,7 +3713,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>29</v>
       </c>
@@ -3724,7 +3727,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>33</v>
       </c>
@@ -3738,7 +3741,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>24</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>64</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>6</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>18</v>
       </c>
@@ -3794,7 +3797,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>29</v>
       </c>
@@ -3808,7 +3811,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>33</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>14</v>
       </c>
@@ -3836,7 +3839,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>64</v>
       </c>
@@ -3850,7 +3853,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>6</v>
       </c>
@@ -3864,7 +3867,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>6</v>
       </c>
@@ -3878,7 +3881,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>85</v>
       </c>
@@ -3892,7 +3895,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>85</v>
       </c>
@@ -3906,7 +3909,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>85</v>
       </c>
@@ -3920,7 +3923,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>85</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>14</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>33</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>6</v>
       </c>
@@ -3976,7 +3979,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>64</v>
       </c>
@@ -3990,7 +3993,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>18</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>29</v>
       </c>
@@ -4018,7 +4021,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>14</v>
       </c>
@@ -4032,7 +4035,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>24</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>18</v>
       </c>
@@ -4060,7 +4063,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>33</v>
       </c>
@@ -4074,7 +4077,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>6</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>64</v>
       </c>
@@ -4102,7 +4105,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>85</v>
       </c>
@@ -4128,32 +4131,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="5">
         <v>46261</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>287</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>288</v>
       </c>
@@ -4202,7 +4205,7 @@
         <v>290</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>289</v>
@@ -4223,7 +4226,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>296</v>
       </c>
@@ -4258,7 +4261,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>296</v>
       </c>
@@ -4270,7 +4273,7 @@
       </c>
       <c r="G8" s="4"/>
       <c r="H8" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
@@ -4279,7 +4282,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>303</v>
       </c>
@@ -4312,7 +4315,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>308</v>
       </c>
@@ -4337,7 +4340,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>310</v>
       </c>
@@ -4372,7 +4375,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>312</v>
       </c>
@@ -4407,7 +4410,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>314</v>
       </c>
@@ -4442,7 +4445,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>317</v>
       </c>
@@ -4472,10 +4475,10 @@
         <v>321</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>317</v>
       </c>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>323</v>
       </c>
@@ -4535,7 +4538,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>330</v>
       </c>
@@ -4570,7 +4573,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>332</v>
       </c>
@@ -4603,7 +4606,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>336</v>
       </c>
@@ -4627,7 +4630,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>341</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>343</v>
       </c>
@@ -4663,10 +4666,10 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C23" s="4"/>
     </row>
   </sheetData>
@@ -4677,14 +4680,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="44.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" customWidth="1"/>
+    <col min="5" max="5" width="44.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>448</v>
       </c>
@@ -4698,7 +4701,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>6</v>
       </c>
@@ -4712,7 +4715,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -4726,7 +4729,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>18</v>
       </c>
@@ -4740,7 +4743,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>33</v>
       </c>
@@ -4754,7 +4757,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>64</v>
       </c>
@@ -4768,7 +4771,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>24</v>
       </c>
@@ -4796,7 +4799,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>131</v>
       </c>
@@ -4810,7 +4813,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>21</v>
       </c>
@@ -4824,7 +4827,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>70</v>
       </c>
@@ -4838,7 +4841,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -4852,7 +4855,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>85</v>
       </c>
@@ -4874,7 +4877,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4885,7 +4888,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>486</v>
       </c>
@@ -4897,8 +4900,8 @@
       <c r="G1" s="27"/>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -4924,7 +4927,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4950,7 +4953,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4976,7 +4979,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -5002,7 +5005,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -5028,7 +5031,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5054,7 +5057,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -5080,7 +5083,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -5106,7 +5109,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5132,7 +5135,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -5158,7 +5161,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -5184,7 +5187,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -5210,7 +5213,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5236,7 +5239,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -5262,7 +5265,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -5288,7 +5291,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -5314,7 +5317,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -5340,7 +5343,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -5366,7 +5369,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -5418,7 +5421,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -5444,7 +5447,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -5470,7 +5473,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -5496,7 +5499,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -5522,7 +5525,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -5548,7 +5551,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -5574,7 +5577,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -5600,7 +5603,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -5626,7 +5629,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -5652,7 +5655,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -5704,7 +5707,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -5730,7 +5733,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -5756,7 +5759,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -5808,7 +5811,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -5834,7 +5837,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -5860,7 +5863,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -5886,7 +5889,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -5912,7 +5915,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -5938,7 +5941,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -5964,7 +5967,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -5990,7 +5993,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -6016,7 +6019,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -6042,7 +6045,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -6068,7 +6071,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -6094,7 +6097,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -6120,7 +6123,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -6146,7 +6149,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -6172,7 +6175,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -6198,7 +6201,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -6224,7 +6227,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -6250,7 +6253,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -6276,7 +6279,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -6302,7 +6305,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6328,7 +6331,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -6354,7 +6357,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -6380,7 +6383,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -6406,7 +6409,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -6432,7 +6435,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -6458,7 +6461,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>29</v>
       </c>
@@ -6484,7 +6487,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>29</v>
       </c>
@@ -6510,7 +6513,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -6536,7 +6539,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>29</v>
       </c>
@@ -6562,7 +6565,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -6588,7 +6591,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -6614,7 +6617,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -6640,7 +6643,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -6666,7 +6669,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -6692,7 +6695,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -6718,7 +6721,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -6744,7 +6747,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -6770,7 +6773,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -6796,7 +6799,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -6874,7 +6877,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>70</v>
       </c>
@@ -6900,7 +6903,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -6926,7 +6929,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>70</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -6978,7 +6981,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>70</v>
       </c>
@@ -7004,7 +7007,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>70</v>
       </c>
@@ -7030,7 +7033,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>70</v>
       </c>
@@ -7056,7 +7059,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>70</v>
       </c>
@@ -7082,7 +7085,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>70</v>
       </c>
@@ -7108,7 +7111,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>70</v>
       </c>
@@ -7134,7 +7137,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>70</v>
       </c>
@@ -7160,7 +7163,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>70</v>
       </c>
@@ -7186,7 +7189,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>70</v>
       </c>
@@ -7212,7 +7215,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>70</v>
       </c>
@@ -7238,7 +7241,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>64</v>
       </c>
@@ -7264,7 +7267,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>64</v>
       </c>
@@ -7290,7 +7293,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>64</v>
       </c>
@@ -7316,7 +7319,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>64</v>
       </c>
@@ -7342,7 +7345,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>64</v>
       </c>
@@ -7368,7 +7371,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>64</v>
       </c>
@@ -7394,7 +7397,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>64</v>
       </c>
@@ -7420,7 +7423,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>64</v>
       </c>
@@ -7446,7 +7449,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -7472,7 +7475,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -7498,7 +7501,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -7524,7 +7527,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>33</v>
       </c>
@@ -7550,7 +7553,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -7576,7 +7579,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -7628,12 +7631,12 @@
         <v>507</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A3:H113" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
@@ -7646,24 +7649,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:F71"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="18" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="18" customWidth="1"/>
     <col min="2" max="2" width="12" style="18" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="18" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="18" customWidth="1"/>
-    <col min="6" max="6" width="98.140625" style="18" customWidth="1"/>
-    <col min="7" max="18" width="8.85546875" style="18" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="18"/>
+    <col min="3" max="3" width="46.5546875" style="18" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="18" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="18" customWidth="1"/>
+    <col min="6" max="6" width="98.109375" style="18" customWidth="1"/>
+    <col min="7" max="18" width="8.88671875" style="18" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
         <v>345</v>
       </c>
@@ -7680,7 +7683,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="18" t="s">
         <v>29</v>
       </c>
@@ -7691,7 +7694,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="18" t="s">
         <v>29</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="18" t="s">
         <v>29</v>
       </c>
@@ -7716,7 +7719,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>29</v>
       </c>
@@ -7730,7 +7733,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>29</v>
       </c>
@@ -7741,7 +7744,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>29</v>
       </c>
@@ -7752,7 +7755,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>29</v>
       </c>
@@ -7766,7 +7769,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>29</v>
       </c>
@@ -7777,7 +7780,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>24</v>
       </c>
@@ -7794,7 +7797,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
@@ -7808,7 +7811,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="18" t="s">
         <v>24</v>
       </c>
@@ -7822,7 +7825,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>24</v>
       </c>
@@ -7836,7 +7839,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
         <v>24</v>
       </c>
@@ -7850,7 +7853,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>24</v>
       </c>
@@ -7864,7 +7867,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="21" t="s">
         <v>24</v>
       </c>
@@ -7877,7 +7880,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
         <v>64</v>
       </c>
@@ -7891,7 +7894,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
         <v>64</v>
       </c>
@@ -7905,7 +7908,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
         <v>64</v>
       </c>
@@ -7919,7 +7922,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
         <v>64</v>
       </c>
@@ -7933,7 +7936,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="21" t="s">
         <v>64</v>
       </c>
@@ -7946,7 +7949,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="21" t="s">
         <v>64</v>
       </c>
@@ -7959,7 +7962,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="21" t="s">
         <v>64</v>
       </c>
@@ -7972,7 +7975,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="21" t="s">
         <v>64</v>
       </c>
@@ -7985,7 +7988,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>18</v>
       </c>
@@ -7999,7 +8002,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="18" t="s">
         <v>18</v>
       </c>
@@ -8011,7 +8014,7 @@
       </c>
       <c r="E28" s="20"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>18</v>
       </c>
@@ -8023,7 +8026,7 @@
       </c>
       <c r="E29" s="20"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
         <v>18</v>
       </c>
@@ -8035,7 +8038,7 @@
       </c>
       <c r="E30" s="20"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>18</v>
       </c>
@@ -8047,7 +8050,7 @@
       </c>
       <c r="E31" s="20"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
         <v>18</v>
       </c>
@@ -8059,7 +8062,7 @@
       </c>
       <c r="E32" s="20"/>
     </row>
-    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="18" t="s">
         <v>18</v>
       </c>
@@ -8076,7 +8079,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="18" t="s">
         <v>18</v>
       </c>
@@ -8093,7 +8096,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="18" t="s">
         <v>33</v>
       </c>
@@ -8108,7 +8111,7 @@
       </c>
       <c r="F35" s="23"/>
     </row>
-    <row r="36" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="18" t="s">
         <v>33</v>
       </c>
@@ -8123,7 +8126,7 @@
       </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="21" t="s">
         <v>33</v>
       </c>
@@ -8136,7 +8139,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="15"/>
     </row>
-    <row r="38" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="21" t="s">
         <v>33</v>
       </c>
@@ -8149,7 +8152,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="15"/>
     </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="18" t="s">
         <v>33</v>
       </c>
@@ -8163,7 +8166,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="21" t="s">
         <v>33</v>
       </c>
@@ -8176,7 +8179,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
@@ -8193,7 +8196,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="18" t="s">
         <v>85</v>
       </c>
@@ -8207,7 +8210,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="18" t="s">
         <v>85</v>
       </c>
@@ -8221,7 +8224,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="18" t="s">
         <v>6</v>
       </c>
@@ -8235,7 +8238,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="18" t="s">
         <v>6</v>
       </c>
@@ -8249,7 +8252,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="18" t="s">
         <v>6</v>
       </c>
@@ -8263,7 +8266,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="18" t="s">
         <v>6</v>
       </c>
@@ -8274,7 +8277,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="18" t="s">
         <v>6</v>
       </c>
@@ -8285,7 +8288,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="21" t="s">
         <v>21</v>
       </c>
@@ -8298,7 +8301,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="21"/>
     </row>
-    <row r="50" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="21" t="s">
         <v>21</v>
       </c>
@@ -8311,7 +8314,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="21"/>
     </row>
-    <row r="51" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="21" t="s">
         <v>21</v>
       </c>
@@ -8324,7 +8327,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="21"/>
     </row>
-    <row r="52" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="21" t="s">
         <v>21</v>
       </c>
@@ -8337,7 +8340,7 @@
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
     </row>
-    <row r="53" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="21" t="s">
         <v>21</v>
       </c>
@@ -8350,7 +8353,7 @@
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
     </row>
-    <row r="54" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="21" t="s">
         <v>21</v>
       </c>
@@ -8363,7 +8366,7 @@
       <c r="E54" s="21"/>
       <c r="F54" s="21"/>
     </row>
-    <row r="55" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="21" t="s">
         <v>21</v>
       </c>
@@ -8376,7 +8379,7 @@
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
     </row>
-    <row r="56" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="21" t="s">
         <v>21</v>
       </c>
@@ -8389,7 +8392,7 @@
       <c r="E56" s="21"/>
       <c r="F56" s="21"/>
     </row>
-    <row r="57" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="21" t="s">
         <v>21</v>
       </c>
@@ -8402,7 +8405,7 @@
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
     </row>
-    <row r="58" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="21" t="s">
         <v>21</v>
       </c>
@@ -8415,7 +8418,7 @@
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
     </row>
-    <row r="59" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="21" t="s">
         <v>21</v>
       </c>
@@ -8428,7 +8431,7 @@
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
     </row>
-    <row r="60" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="21" t="s">
         <v>21</v>
       </c>
@@ -8441,7 +8444,7 @@
       <c r="E60" s="21"/>
       <c r="F60" s="21"/>
     </row>
-    <row r="61" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="21" t="s">
         <v>21</v>
       </c>
@@ -8454,7 +8457,7 @@
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
     </row>
-    <row r="62" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="21" t="s">
         <v>70</v>
       </c>
@@ -8467,7 +8470,7 @@
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
     </row>
-    <row r="63" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="21" t="s">
         <v>70</v>
       </c>
@@ -8480,7 +8483,7 @@
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
     </row>
-    <row r="64" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="21" t="s">
         <v>70</v>
       </c>
@@ -8493,7 +8496,7 @@
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
     </row>
-    <row r="65" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="21" t="s">
         <v>70</v>
       </c>
@@ -8506,7 +8509,7 @@
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
     </row>
-    <row r="66" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="21" t="s">
         <v>70</v>
       </c>
@@ -8519,7 +8522,7 @@
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
     </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="21" t="s">
         <v>70</v>
       </c>
@@ -8532,7 +8535,7 @@
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
     </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="21" t="s">
         <v>14</v>
       </c>
@@ -8545,7 +8548,7 @@
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
     </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="21" t="s">
         <v>14</v>
       </c>
@@ -8558,7 +8561,7 @@
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="21" t="s">
         <v>14</v>
       </c>
@@ -8571,7 +8574,7 @@
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="21" t="s">
         <v>14</v>
       </c>
@@ -8593,21 +8596,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>695</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
     </row>
-    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -8618,7 +8621,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -8629,7 +8632,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -8640,7 +8643,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -8651,7 +8654,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -8662,7 +8665,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -8673,7 +8676,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -8684,7 +8687,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8695,7 +8698,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -8706,7 +8709,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -8717,7 +8720,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -8728,7 +8731,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -8739,7 +8742,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -8750,7 +8753,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -8761,7 +8764,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -8772,7 +8775,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -8783,7 +8786,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -8794,7 +8797,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -8805,7 +8808,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8816,7 +8819,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -8827,7 +8830,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -8838,7 +8841,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -8849,7 +8852,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -8860,7 +8863,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -8871,7 +8874,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -8882,7 +8885,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -8893,7 +8896,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -8904,7 +8907,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -8915,7 +8918,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -8926,7 +8929,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -8937,7 +8940,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -8948,7 +8951,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -8959,7 +8962,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -8970,7 +8973,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -8981,7 +8984,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -8992,7 +8995,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -9003,7 +9006,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -9014,7 +9017,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -9025,7 +9028,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -9036,7 +9039,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -9047,7 +9050,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -9058,7 +9061,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -9069,7 +9072,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -9080,7 +9083,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -9091,7 +9094,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -9102,7 +9105,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -9113,7 +9116,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -9124,7 +9127,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -9135,7 +9138,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -9146,7 +9149,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -9157,7 +9160,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -9168,7 +9171,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -9179,7 +9182,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -9190,7 +9193,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -9201,7 +9204,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -9212,7 +9215,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -9223,7 +9226,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -9234,7 +9237,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -9245,7 +9248,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -9256,7 +9259,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -9267,7 +9270,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -9278,7 +9281,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -9289,7 +9292,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -9300,7 +9303,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9311,7 +9314,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9322,7 +9325,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9333,7 +9336,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9344,7 +9347,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9355,7 +9358,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9366,7 +9369,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -9377,7 +9380,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9388,7 +9391,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -9399,7 +9402,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -9410,7 +9413,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -9421,7 +9424,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>29</v>
       </c>
@@ -9432,7 +9435,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>29</v>
       </c>
@@ -9443,7 +9446,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>29</v>
       </c>
@@ -9454,7 +9457,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -9465,7 +9468,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -9476,7 +9479,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>29</v>
       </c>
@@ -9487,7 +9490,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -9498,7 +9501,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>29</v>
       </c>
@@ -9509,7 +9512,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -9520,7 +9523,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -9531,7 +9534,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -9542,7 +9545,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -9553,7 +9556,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>29</v>
       </c>
@@ -9564,7 +9567,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>29</v>
       </c>
@@ -9575,7 +9578,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
@@ -9586,7 +9589,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -9597,7 +9600,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>21</v>
       </c>
@@ -9608,7 +9611,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -9619,7 +9622,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>21</v>
       </c>
@@ -9630,7 +9633,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>21</v>
       </c>
@@ -9641,7 +9644,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -9652,7 +9655,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>21</v>
       </c>
@@ -9663,7 +9666,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -9674,7 +9677,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>21</v>
       </c>
@@ -9685,7 +9688,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>21</v>
       </c>
@@ -9696,7 +9699,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -9707,7 +9710,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -9718,7 +9721,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>21</v>
       </c>
@@ -9729,7 +9732,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>21</v>
       </c>
@@ -9740,7 +9743,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>21</v>
       </c>
@@ -9751,7 +9754,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>70</v>
       </c>
@@ -9762,7 +9765,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>70</v>
       </c>
@@ -9773,7 +9776,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>70</v>
       </c>
@@ -9784,7 +9787,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>70</v>
       </c>
@@ -9795,7 +9798,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>70</v>
       </c>
@@ -9806,7 +9809,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>70</v>
       </c>
@@ -9817,7 +9820,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>70</v>
       </c>
@@ -9828,7 +9831,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>70</v>
       </c>
@@ -9839,7 +9842,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>70</v>
       </c>
@@ -9850,7 +9853,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>70</v>
       </c>
@@ -9861,7 +9864,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>70</v>
       </c>
@@ -9872,7 +9875,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>70</v>
       </c>
@@ -9883,7 +9886,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>70</v>
       </c>
@@ -9894,7 +9897,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>70</v>
       </c>
@@ -9905,7 +9908,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>70</v>
       </c>
@@ -9916,7 +9919,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>70</v>
       </c>
@@ -9927,7 +9930,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>70</v>
       </c>
@@ -9938,7 +9941,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>70</v>
       </c>
@@ -9949,7 +9952,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>70</v>
       </c>
@@ -9960,7 +9963,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>70</v>
       </c>
@@ -9971,7 +9974,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>70</v>
       </c>
@@ -9982,7 +9985,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -9993,7 +9996,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>64</v>
       </c>
@@ -10004,7 +10007,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>64</v>
       </c>
@@ -10015,7 +10018,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>64</v>
       </c>
@@ -10026,7 +10029,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>64</v>
       </c>
@@ -10037,7 +10040,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>64</v>
       </c>
@@ -10048,7 +10051,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>64</v>
       </c>
@@ -10059,7 +10062,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>64</v>
       </c>
@@ -10070,7 +10073,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>64</v>
       </c>
@@ -10081,7 +10084,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>64</v>
       </c>
@@ -10092,7 +10095,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>64</v>
       </c>
@@ -10103,7 +10106,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>64</v>
       </c>
@@ -10114,7 +10117,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>64</v>
       </c>
@@ -10125,7 +10128,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>64</v>
       </c>
@@ -10136,7 +10139,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>64</v>
       </c>
@@ -10147,7 +10150,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>64</v>
       </c>
@@ -10158,7 +10161,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>64</v>
       </c>
@@ -10169,7 +10172,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>64</v>
       </c>
@@ -10180,7 +10183,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>64</v>
       </c>
@@ -10191,7 +10194,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>64</v>
       </c>
@@ -10202,7 +10205,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>64</v>
       </c>
@@ -10213,7 +10216,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>64</v>
       </c>
@@ -10224,7 +10227,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>64</v>
       </c>
@@ -10235,7 +10238,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>64</v>
       </c>
@@ -10246,7 +10249,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>64</v>
       </c>
@@ -10257,7 +10260,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>64</v>
       </c>
@@ -10268,7 +10271,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>64</v>
       </c>
@@ -10279,7 +10282,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>64</v>
       </c>
@@ -10290,7 +10293,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>64</v>
       </c>
@@ -10301,7 +10304,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>64</v>
       </c>
@@ -10312,7 +10315,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>64</v>
       </c>
@@ -10323,7 +10326,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>64</v>
       </c>
@@ -10334,7 +10337,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>33</v>
       </c>
@@ -10345,7 +10348,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>33</v>
       </c>
@@ -10356,7 +10359,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>33</v>
       </c>
@@ -10367,7 +10370,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -10378,7 +10381,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>33</v>
       </c>
@@ -10389,7 +10392,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>33</v>
       </c>
@@ -10400,7 +10403,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>33</v>
       </c>
@@ -10411,7 +10414,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>33</v>
       </c>
@@ -10422,7 +10425,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>33</v>
       </c>
@@ -10433,7 +10436,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>33</v>
       </c>
@@ -10444,7 +10447,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>33</v>
       </c>
@@ -10455,7 +10458,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>33</v>
       </c>
@@ -10466,7 +10469,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>33</v>
       </c>
@@ -10477,7 +10480,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>33</v>
       </c>
@@ -10488,7 +10491,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>33</v>
       </c>
@@ -10499,7 +10502,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -10510,13 +10513,13 @@
         <v>408</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A3:C182" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="1">
@@ -10528,8 +10531,8 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10538,7 +10541,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>702</v>
       </c>
@@ -10547,7 +10550,7 @@
       <c r="D1" s="27"/>
       <c r="E1" s="27"/>
     </row>
-    <row r="3" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>345</v>
       </c>
@@ -10564,7 +10567,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -10581,7 +10584,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -10595,7 +10598,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10609,7 +10612,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10626,7 +10629,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -10643,7 +10646,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -10657,7 +10660,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10671,7 +10674,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -10688,7 +10691,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -10702,7 +10705,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -10716,7 +10719,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -10733,7 +10736,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -10747,7 +10750,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -10761,7 +10764,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -10775,7 +10778,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -10789,7 +10792,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -10803,7 +10806,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -10820,7 +10823,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -10834,7 +10837,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -10848,7 +10851,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -10862,7 +10865,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -10876,7 +10879,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -10890,7 +10893,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -10904,7 +10907,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -10918,7 +10921,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -10935,7 +10938,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -10949,7 +10952,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -10966,7 +10969,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
         <v>33</v>
       </c>
@@ -10997,7 +11000,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>33</v>
       </c>
@@ -11012,7 +11015,7 @@
       </c>
       <c r="E33" s="15"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>33</v>
       </c>
@@ -11029,7 +11032,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>33</v>
       </c>
@@ -11044,7 +11047,7 @@
       </c>
       <c r="E35" s="15"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -11061,7 +11064,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -11078,7 +11081,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -11092,7 +11095,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -11109,7 +11112,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -11126,7 +11129,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -11143,7 +11146,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -11157,7 +11160,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -11171,7 +11174,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -11179,16 +11182,16 @@
         <v>360</v>
       </c>
       <c r="C44" t="s">
-        <v>754</v>
+        <v>804</v>
       </c>
       <c r="D44" t="s">
         <v>707</v>
       </c>
       <c r="E44" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -11196,16 +11199,16 @@
         <v>360</v>
       </c>
       <c r="C45" t="s">
-        <v>756</v>
+        <v>805</v>
       </c>
       <c r="D45" t="s">
         <v>707</v>
       </c>
       <c r="E45" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -11213,95 +11216,101 @@
         <v>360</v>
       </c>
       <c r="C46" t="s">
-        <v>757</v>
+        <v>806</v>
       </c>
       <c r="D46" t="s">
         <v>707</v>
       </c>
       <c r="E46" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>698</v>
+        <v>360</v>
       </c>
       <c r="C47" t="s">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="D47" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>367</v>
+        <v>698</v>
       </c>
       <c r="C48" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="D48" t="s">
         <v>707</v>
       </c>
       <c r="E48" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="D49" t="s">
         <v>707</v>
       </c>
       <c r="E49" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C50" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="D50" t="s">
         <v>707</v>
       </c>
       <c r="E50" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C51" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="D51" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -11309,13 +11318,13 @@
         <v>373</v>
       </c>
       <c r="C52" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="D52" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -11323,92 +11332,89 @@
         <v>373</v>
       </c>
       <c r="C53" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="D53" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C54" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D54" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C55" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="D55" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C56" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="D56" t="s">
         <v>707</v>
       </c>
-      <c r="E56" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C57" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="D57" t="s">
         <v>707</v>
       </c>
       <c r="E57" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C58" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="D58" t="s">
         <v>707</v>
       </c>
       <c r="E58" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -11416,27 +11422,30 @@
         <v>382</v>
       </c>
       <c r="C59" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="D59" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+      <c r="E59" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C60" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D60" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -11444,65 +11453,79 @@
         <v>384</v>
       </c>
       <c r="C61" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="D61" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C62" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="D62" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C63" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D63" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C64" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="D64" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>388</v>
+      </c>
+      <c r="C65" t="s">
+        <v>774</v>
+      </c>
+      <c r="D65" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
         <v>389</v>
       </c>
-      <c r="C65" t="s">
-        <v>779</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="C66" t="s">
+        <v>775</v>
+      </c>
+      <c r="D66" t="s">
         <v>707</v>
       </c>
     </row>
@@ -11517,7 +11540,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -11526,99 +11549,99 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>780</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>781</v>
       </c>
-      <c r="C1" s="11" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>782</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>783</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>784</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>786</v>
       </c>
       <c r="B2" s="12">
         <v>46184</v>
       </c>
       <c r="C2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="E2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B3" s="12">
         <v>46184</v>
       </c>
       <c r="C3" t="s">
+        <v>783</v>
+      </c>
+      <c r="D3" t="s">
         <v>787</v>
       </c>
-      <c r="D3" t="s">
-        <v>791</v>
-      </c>
       <c r="E3" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B4" s="12">
         <v>46184</v>
       </c>
       <c r="C4" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D4" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E4" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B5" s="12">
         <v>46184</v>
       </c>
       <c r="C5" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D5" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E5" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>692694</v>
       </c>
@@ -11626,16 +11649,16 @@
         <v>46185</v>
       </c>
       <c r="C6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E6" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>708274</v>
       </c>
@@ -11643,16 +11666,16 @@
         <v>46273</v>
       </c>
       <c r="C7" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D7" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E7" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>691920</v>
       </c>
@@ -11660,16 +11683,16 @@
         <v>46273</v>
       </c>
       <c r="C8" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D8" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E8" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>691923</v>
       </c>
@@ -11677,16 +11700,16 @@
         <v>46273</v>
       </c>
       <c r="C9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D9" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E9" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>701797</v>
       </c>
@@ -11694,16 +11717,16 @@
         <v>46273</v>
       </c>
       <c r="C10" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D10" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E10" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>701540</v>
       </c>
@@ -11711,16 +11734,16 @@
         <v>46273</v>
       </c>
       <c r="C11" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D11" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E11" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>692683</v>
       </c>
@@ -11728,13 +11751,13 @@
         <v>46273</v>
       </c>
       <c r="C12" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D12" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E12" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -11750,16 +11773,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A2:E89"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -11773,7 +11796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -11787,7 +11810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -11801,7 +11824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -11815,7 +11838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -11829,7 +11852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -11843,7 +11866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -11857,7 +11880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>4</v>
       </c>
@@ -11871,7 +11894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>4</v>
       </c>
@@ -11885,7 +11908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -11899,7 +11922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>4</v>
       </c>
@@ -11913,7 +11936,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>4</v>
       </c>
@@ -11927,7 +11950,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>4</v>
       </c>
@@ -11941,7 +11964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>4</v>
       </c>
@@ -11955,7 +11978,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>4</v>
       </c>
@@ -11969,7 +11992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>4</v>
       </c>
@@ -11983,7 +12006,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -11997,7 +12020,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="7">
         <v>46092</v>
       </c>
@@ -12011,7 +12034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="7">
         <v>46092</v>
       </c>
@@ -12025,7 +12048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="7">
         <v>46092</v>
       </c>
@@ -12039,7 +12062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="7">
         <v>46092</v>
       </c>
@@ -12053,7 +12076,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="7">
         <v>46092</v>
       </c>
@@ -12067,7 +12090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="7">
         <v>46092</v>
       </c>
@@ -12081,7 +12104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="7">
         <v>46092</v>
       </c>
@@ -12095,7 +12118,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="7">
         <v>46119</v>
       </c>
@@ -12109,7 +12132,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="7">
         <v>46119</v>
       </c>
@@ -12123,7 +12146,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="7">
         <v>46119</v>
       </c>
@@ -12137,7 +12160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="7">
         <v>46119</v>
       </c>
@@ -12151,7 +12174,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="7">
         <v>46121</v>
       </c>
@@ -12165,7 +12188,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="7">
         <v>46121</v>
       </c>
@@ -12179,7 +12202,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="7">
         <v>46126</v>
       </c>
@@ -12193,7 +12216,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="7">
         <v>46134</v>
       </c>
@@ -12207,7 +12230,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="7">
         <v>46134</v>
       </c>
@@ -12221,7 +12244,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="7">
         <v>46142</v>
       </c>
@@ -12235,7 +12258,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="7">
         <v>46160</v>
       </c>
@@ -12249,7 +12272,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="7">
         <v>46169</v>
       </c>
@@ -12263,7 +12286,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="7">
         <v>46170</v>
       </c>
@@ -12277,7 +12300,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="7">
         <v>46170</v>
       </c>
@@ -12291,7 +12314,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="7">
         <v>46170</v>
       </c>
@@ -12305,7 +12328,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="7">
         <v>46171</v>
       </c>
@@ -12319,7 +12342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="7">
         <v>46171</v>
       </c>
@@ -12333,7 +12356,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="7">
         <v>46171</v>
       </c>
@@ -12347,7 +12370,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="7">
         <v>46171</v>
       </c>
@@ -12361,7 +12384,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="7">
         <v>46171</v>
       </c>
@@ -12375,7 +12398,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="7">
         <v>46175</v>
       </c>
@@ -12389,7 +12412,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="7">
         <v>46175</v>
       </c>
@@ -12403,7 +12426,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="7">
         <v>46175</v>
       </c>
@@ -12417,7 +12440,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="7">
         <v>46175</v>
       </c>
@@ -12431,7 +12454,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="7">
         <v>46175</v>
       </c>
@@ -12445,7 +12468,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="7">
         <v>46175</v>
       </c>
@@ -12459,7 +12482,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="7">
         <v>46178</v>
       </c>
@@ -12473,7 +12496,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="7">
         <v>46178</v>
       </c>
@@ -12487,7 +12510,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="7">
         <v>46178</v>
       </c>
@@ -12501,7 +12524,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" s="7">
         <v>46178</v>
       </c>
@@ -12515,7 +12538,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="7">
         <v>46178</v>
       </c>
@@ -12529,7 +12552,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="7">
         <v>46184</v>
       </c>
@@ -12543,7 +12566,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="7">
         <v>46188</v>
       </c>
@@ -12557,7 +12580,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="7">
         <v>46189</v>
       </c>
@@ -12571,7 +12594,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="7">
         <v>46189</v>
       </c>
@@ -12585,7 +12608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="7">
         <v>46211</v>
       </c>
@@ -12599,7 +12622,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" s="7">
         <v>46212</v>
       </c>
@@ -12613,7 +12636,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63" s="7">
         <v>46212</v>
       </c>
@@ -12627,7 +12650,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" s="7">
         <v>46212</v>
       </c>
@@ -12641,7 +12664,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B65" s="7">
         <v>46212</v>
       </c>
@@ -12655,7 +12678,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B66" s="7">
         <v>46212</v>
       </c>
@@ -12669,7 +12692,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B67" s="7">
         <v>46212</v>
       </c>
@@ -12683,7 +12706,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B68" s="7">
         <v>46212</v>
       </c>
@@ -12697,7 +12720,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B69" s="7">
         <v>46212</v>
       </c>
@@ -12711,7 +12734,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B70" s="7">
         <v>46212</v>
       </c>
@@ -12725,7 +12748,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B71" s="7">
         <v>46216</v>
       </c>
@@ -12739,7 +12762,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B72" s="7">
         <v>46216</v>
       </c>
@@ -12753,7 +12776,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B73" s="7">
         <v>46216</v>
       </c>
@@ -12767,7 +12790,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B74" s="7">
         <v>46225</v>
       </c>
@@ -12781,7 +12804,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B75" s="7">
         <v>46240</v>
       </c>
@@ -12795,7 +12818,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B76" s="7">
         <v>46240</v>
       </c>
@@ -12809,7 +12832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B77" s="7">
         <v>46245</v>
       </c>
@@ -12823,7 +12846,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B78" s="7">
         <v>46246</v>
       </c>
@@ -12837,7 +12860,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="15"/>
       <c r="B79" s="16">
         <v>46247</v>
@@ -12852,7 +12875,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B80" s="16">
         <v>46251</v>
       </c>
@@ -12866,7 +12889,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="16">
         <v>46253</v>
       </c>
@@ -12880,7 +12903,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="16">
         <v>46253</v>
       </c>
@@ -12894,7 +12917,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="16">
         <v>46253</v>
       </c>
@@ -12905,10 +12928,10 @@
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="16">
         <v>46253</v>
       </c>
@@ -12919,10 +12942,10 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="16">
         <v>46253</v>
       </c>
@@ -12933,10 +12956,10 @@
         <v>33</v>
       </c>
       <c r="E85" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="16">
         <v>46253</v>
       </c>
@@ -12947,10 +12970,10 @@
         <v>64</v>
       </c>
       <c r="E86" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="16">
         <v>46253</v>
       </c>
@@ -12961,10 +12984,10 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="16">
         <v>46253</v>
       </c>
@@ -12978,7 +13001,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="16">
         <v>46253</v>
       </c>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58561800-C70F-4911-99FB-F0513FB7635C}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E92CA9-8615-4C61-89EA-86D0A29E50DE}"/>
   <bookViews>
-    <workbookView xWindow="45885" yWindow="2490" windowWidth="27450" windowHeight="15285" tabRatio="819" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="change log" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$F$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">productos_resultados!$A$3:$C$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">resultados!$A$3:$H$113</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="811">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2462,6 +2462,12 @@
   </si>
   <si>
     <t>Modelo desarrollado. Implementación requiere finalización de CCP que están en proceso de licitación.</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000193-1079781365-43</t>
+  </si>
+  <si>
+    <t>PEP Agua Potable y Saneamiento I sem 2026</t>
   </si>
 </sst>
 </file>
@@ -2633,7 +2639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2692,14 +2698,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3035,7 +3046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="8" customWidth="1"/>
@@ -3047,12 +3058,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3169,296 +3180,296 @@
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>144</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>146</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>174</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>174</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>174</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>174</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>174</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>184</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3466,27 +3477,27 @@
         <v>14</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>186</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>189</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3494,41 +3505,41 @@
         <v>6</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>191</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>194</v>
+        <v>267</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>195</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3536,531 +3547,531 @@
         <v>29</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>197</v>
+        <v>269</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>199</v>
+        <v>810</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>222</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>226</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>218</v>
+        <v>142</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>232</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>234</v>
+        <v>145</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>235</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>237</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>240</v>
+        <v>151</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>242</v>
+        <v>153</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>243</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>89</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>218</v>
+        <v>271</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>126</v>
+        <v>271</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="D71" t="s">
-        <v>270</v>
+        <v>219</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>273</v>
+        <v>221</v>
+      </c>
+      <c r="D72" s="29" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -4068,27 +4079,27 @@
         <v>33</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>281</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -4096,13 +4107,13 @@
         <v>64</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -4110,17 +4121,35 @@
         <v>85</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>285</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:D60" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:D79">
+      <sortCondition ref="B3:B60"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -4889,16 +4918,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8603,11 +8632,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>695</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -10542,13 +10571,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>702</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E92CA9-8615-4C61-89EA-86D0A29E50DE}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B02447-C743-407D-8B91-E6031B2E34AF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,12 +750,6 @@
     <t>https://idbg.sharepoint.com/teams/EZ-CR-LON/CR-L1065/_layouts/15/DocIdRedir.aspx?ID=EZIDB0000195-998400382-110</t>
   </si>
   <si>
-    <t>EZIDB0000195-822257051-222</t>
-  </si>
-  <si>
-    <t>https://idbg.sharepoint.com/teams/EZ-CR-LON/CR-L1137/_layouts/15/DocIdRedir.aspx?ID=EZIDB0000195-822257051-222</t>
-  </si>
-  <si>
     <t>EZIDB0000195-1127813953-75</t>
   </si>
   <si>
@@ -2468,6 +2462,12 @@
   </si>
   <si>
     <t>PEP Agua Potable y Saneamiento I sem 2026</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-1647385829-102</t>
+  </si>
+  <si>
+    <t>Plan financiero CR-L1137 sept 2026</t>
   </si>
 </sst>
 </file>
@@ -2698,18 +2698,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3186,10 +3186,10 @@
         <v>126</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3200,10 +3200,10 @@
         <v>126</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3340,10 +3340,10 @@
         <v>187</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3351,13 +3351,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3463,10 +3463,10 @@
         <v>6</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>89</v>
@@ -3477,13 +3477,13 @@
         <v>14</v>
       </c>
       <c r="B32" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3491,13 +3491,13 @@
         <v>33</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3505,13 +3505,13 @@
         <v>6</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3519,13 +3519,13 @@
         <v>64</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3533,13 +3533,13 @@
         <v>18</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3547,13 +3547,13 @@
         <v>29</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>270</v>
+        <v>267</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3561,13 +3561,13 @@
         <v>85</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>810</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>809</v>
+        <v>808</v>
+      </c>
+      <c r="D38" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3606,10 +3606,10 @@
         <v>233</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>239</v>
+        <v>810</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3620,10 +3620,10 @@
         <v>233</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3869,13 +3869,13 @@
         <v>14</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -3883,13 +3883,13 @@
         <v>24</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -3897,13 +3897,13 @@
         <v>18</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -3911,13 +3911,13 @@
         <v>33</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -3925,13 +3925,13 @@
         <v>6</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -3939,13 +3939,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -3953,13 +3953,13 @@
         <v>85</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -4042,7 +4042,7 @@
       <c r="C72" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D72" s="25" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4124,10 +4124,10 @@
         <v>218</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -4135,13 +4135,13 @@
         <v>85</v>
       </c>
       <c r="B79" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D79" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4177,7 +4177,7 @@
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
@@ -4187,7 +4187,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>6</v>
@@ -4222,131 +4222,131 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="L7" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>306</v>
-      </c>
       <c r="I9" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>306</v>
-      </c>
       <c r="K9" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4354,317 +4354,317 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J10" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>306</v>
-      </c>
       <c r="L10" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>316</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="G14" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>320</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="G16" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>328</v>
-      </c>
       <c r="I16" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="I18" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="G19" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -4672,19 +4672,19 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -4718,16 +4718,16 @@
   <sheetData>
     <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>449</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -4735,13 +4735,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E2" t="s">
         <v>452</v>
-      </c>
-      <c r="D2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
@@ -4749,13 +4749,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -4763,13 +4763,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D4" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" t="s">
         <v>456</v>
-      </c>
-      <c r="D4" t="s">
-        <v>457</v>
-      </c>
-      <c r="E4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -4777,13 +4777,13 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E5" t="s">
         <v>459</v>
-      </c>
-      <c r="D5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E5" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -4791,13 +4791,13 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E6" t="s">
         <v>462</v>
-      </c>
-      <c r="D6" t="s">
-        <v>463</v>
-      </c>
-      <c r="E6" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -4805,13 +4805,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E7" t="s">
         <v>465</v>
-      </c>
-      <c r="D7" t="s">
-        <v>466</v>
-      </c>
-      <c r="E7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -4819,13 +4819,13 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" t="s">
+        <v>467</v>
+      </c>
+      <c r="E8" t="s">
         <v>468</v>
-      </c>
-      <c r="D8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E8" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -4833,13 +4833,13 @@
         <v>131</v>
       </c>
       <c r="C9" t="s">
+        <v>469</v>
+      </c>
+      <c r="D9" t="s">
+        <v>470</v>
+      </c>
+      <c r="E9" t="s">
         <v>471</v>
-      </c>
-      <c r="D9" t="s">
-        <v>472</v>
-      </c>
-      <c r="E9" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -4847,13 +4847,13 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E10" t="s">
         <v>474</v>
-      </c>
-      <c r="D10" t="s">
-        <v>475</v>
-      </c>
-      <c r="E10" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -4861,13 +4861,13 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D11" t="s">
+        <v>476</v>
+      </c>
+      <c r="E11" t="s">
         <v>477</v>
-      </c>
-      <c r="D11" t="s">
-        <v>478</v>
-      </c>
-      <c r="E11" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -4875,13 +4875,13 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
+        <v>478</v>
+      </c>
+      <c r="D12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E12" t="s">
         <v>480</v>
-      </c>
-      <c r="D12" t="s">
-        <v>481</v>
-      </c>
-      <c r="E12" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -4889,13 +4889,13 @@
         <v>85</v>
       </c>
       <c r="C13" t="s">
+        <v>481</v>
+      </c>
+      <c r="D13" t="s">
+        <v>482</v>
+      </c>
+      <c r="E13" t="s">
         <v>483</v>
-      </c>
-      <c r="D13" t="s">
-        <v>484</v>
-      </c>
-      <c r="E13" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -4918,42 +4918,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="A1" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D3" t="s">
         <v>487</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>488</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>489</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>490</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>491</v>
-      </c>
-      <c r="G3" t="s">
-        <v>492</v>
-      </c>
-      <c r="H3" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4961,16 +4961,16 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D4" t="s">
         <v>494</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>495</v>
-      </c>
-      <c r="D4" t="s">
-        <v>496</v>
-      </c>
-      <c r="E4" t="s">
-        <v>497</v>
       </c>
       <c r="F4">
         <v>477</v>
@@ -4979,7 +4979,7 @@
         <v>200</v>
       </c>
       <c r="H4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4987,16 +4987,16 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F5">
         <v>3443</v>
@@ -5005,7 +5005,7 @@
         <v>2500</v>
       </c>
       <c r="H5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5013,16 +5013,16 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5031,7 +5031,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5039,16 +5039,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C7" t="s">
+        <v>502</v>
+      </c>
+      <c r="D7" t="s">
         <v>503</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>504</v>
-      </c>
-      <c r="D7" t="s">
-        <v>505</v>
-      </c>
-      <c r="E7" t="s">
-        <v>506</v>
       </c>
       <c r="F7">
         <v>188</v>
@@ -5057,7 +5057,7 @@
         <v>174</v>
       </c>
       <c r="H7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5065,16 +5065,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D8" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E8" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F8">
         <v>8.6999999999999993</v>
@@ -5083,7 +5083,7 @@
         <v>7.4</v>
       </c>
       <c r="H8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5091,16 +5091,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D9" t="s">
         <v>510</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>511</v>
-      </c>
-      <c r="D9" t="s">
-        <v>512</v>
-      </c>
-      <c r="E9" t="s">
-        <v>513</v>
       </c>
       <c r="F9">
         <v>22338</v>
@@ -5109,7 +5109,7 @@
         <v>14600</v>
       </c>
       <c r="H9" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5117,16 +5117,16 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C10" t="s">
+        <v>512</v>
+      </c>
+      <c r="D10" t="s">
         <v>494</v>
       </c>
-      <c r="C10" t="s">
-        <v>514</v>
-      </c>
-      <c r="D10" t="s">
-        <v>496</v>
-      </c>
       <c r="E10" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -5135,7 +5135,7 @@
         <v>0.5</v>
       </c>
       <c r="H10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5143,16 +5143,16 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C11" t="s">
+        <v>512</v>
+      </c>
+      <c r="D11" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" t="s">
         <v>514</v>
-      </c>
-      <c r="D11" t="s">
-        <v>499</v>
-      </c>
-      <c r="E11" t="s">
-        <v>516</v>
       </c>
       <c r="F11">
         <v>6.5</v>
@@ -5161,7 +5161,7 @@
         <v>5.5</v>
       </c>
       <c r="H11" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5169,16 +5169,16 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -5187,7 +5187,7 @@
         <v>1.6</v>
       </c>
       <c r="H12" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5195,16 +5195,16 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E13" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5221,16 +5221,16 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
+        <v>492</v>
+      </c>
+      <c r="C14" t="s">
+        <v>519</v>
+      </c>
+      <c r="D14" t="s">
         <v>494</v>
       </c>
-      <c r="C14" t="s">
-        <v>521</v>
-      </c>
-      <c r="D14" t="s">
-        <v>496</v>
-      </c>
       <c r="E14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F14">
         <v>0.23799999999999999</v>
@@ -5239,7 +5239,7 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="H14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5247,16 +5247,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D15" t="s">
+        <v>497</v>
+      </c>
+      <c r="E15" t="s">
         <v>521</v>
-      </c>
-      <c r="D15" t="s">
-        <v>499</v>
-      </c>
-      <c r="E15" t="s">
-        <v>523</v>
       </c>
       <c r="F15">
         <v>0.314</v>
@@ -5265,7 +5265,7 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="H15" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5273,16 +5273,16 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C16" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D16" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F16">
         <v>0.82</v>
@@ -5291,7 +5291,7 @@
         <v>0.68799999999999994</v>
       </c>
       <c r="H16" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5299,16 +5299,16 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C17" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F17">
         <v>0.70399999999999996</v>
@@ -5317,7 +5317,7 @@
         <v>0.61399999999999999</v>
       </c>
       <c r="H17" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5325,16 +5325,16 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D18" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E18" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F18">
         <v>1.004</v>
@@ -5343,7 +5343,7 @@
         <v>0.94699999999999995</v>
       </c>
       <c r="H18" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5351,16 +5351,16 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D19" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E19" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F19">
         <v>1.5129999999999999</v>
@@ -5369,7 +5369,7 @@
         <v>1.3220000000000001</v>
       </c>
       <c r="H19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5377,16 +5377,16 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C20" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D20" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E20" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F20">
         <v>0.35799999999999998</v>
@@ -5395,7 +5395,7 @@
         <v>0.249</v>
       </c>
       <c r="H20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5403,16 +5403,16 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D21" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F21">
         <v>0.54100000000000004</v>
@@ -5421,7 +5421,7 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="H21" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5429,16 +5429,16 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D22" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E22" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F22">
         <v>1.5580000000000001</v>
@@ -5447,7 +5447,7 @@
         <v>1.0209999999999999</v>
       </c>
       <c r="H22" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5455,16 +5455,16 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C23" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D23" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E23" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F23">
         <v>1.238</v>
@@ -5473,7 +5473,7 @@
         <v>0.873</v>
       </c>
       <c r="H23" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5481,16 +5481,16 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D24" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E24" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F24">
         <v>1.835</v>
@@ -5499,7 +5499,7 @@
         <v>1.1839999999999999</v>
       </c>
       <c r="H24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5507,16 +5507,16 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C25" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D25" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E25" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F25">
         <v>2.726</v>
@@ -5525,7 +5525,7 @@
         <v>1.3939999999999999</v>
       </c>
       <c r="H25" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5533,16 +5533,16 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C26" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D26" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E26" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F26">
         <v>0.24</v>
@@ -5551,7 +5551,7 @@
         <v>0.24</v>
       </c>
       <c r="H26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5559,16 +5559,16 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C27" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D27" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F27">
         <v>0.31</v>
@@ -5577,7 +5577,7 @@
         <v>0.31</v>
       </c>
       <c r="H27" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5585,16 +5585,16 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C28" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D28" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E28" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F28">
         <v>0.84</v>
@@ -5603,7 +5603,7 @@
         <v>0.71</v>
       </c>
       <c r="H28" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5611,16 +5611,16 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C29" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D29" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E29" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F29">
         <v>0.73</v>
@@ -5629,7 +5629,7 @@
         <v>0.64</v>
       </c>
       <c r="H29" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5637,16 +5637,16 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C30" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D30" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E30" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F30">
         <v>1.02</v>
@@ -5655,7 +5655,7 @@
         <v>0.98</v>
       </c>
       <c r="H30" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5663,16 +5663,16 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C31" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D31" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E31" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F31">
         <v>1.52</v>
@@ -5681,7 +5681,7 @@
         <v>1.36</v>
       </c>
       <c r="H31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5689,16 +5689,16 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
+        <v>501</v>
+      </c>
+      <c r="C32" t="s">
+        <v>552</v>
+      </c>
+      <c r="D32" t="s">
         <v>503</v>
       </c>
-      <c r="C32" t="s">
-        <v>554</v>
-      </c>
-      <c r="D32" t="s">
-        <v>505</v>
-      </c>
       <c r="E32" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F32">
         <v>63</v>
@@ -5707,7 +5707,7 @@
         <v>47</v>
       </c>
       <c r="H32" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5715,16 +5715,16 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C33" t="s">
+        <v>552</v>
+      </c>
+      <c r="D33" t="s">
+        <v>506</v>
+      </c>
+      <c r="E33" t="s">
         <v>554</v>
-      </c>
-      <c r="D33" t="s">
-        <v>508</v>
-      </c>
-      <c r="E33" t="s">
-        <v>556</v>
       </c>
       <c r="F33">
         <v>56</v>
@@ -5733,7 +5733,7 @@
         <v>48</v>
       </c>
       <c r="H33" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5741,16 +5741,16 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C34" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D34" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E34" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F34">
         <v>84</v>
@@ -5759,7 +5759,7 @@
         <v>54</v>
       </c>
       <c r="H34" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5767,16 +5767,16 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C35" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D35" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E35" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F35">
         <v>77</v>
@@ -5785,7 +5785,7 @@
         <v>56</v>
       </c>
       <c r="H35" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5793,16 +5793,16 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C36" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D36" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E36" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F36">
         <v>84</v>
@@ -5811,7 +5811,7 @@
         <v>47</v>
       </c>
       <c r="H36" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5819,16 +5819,16 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C37" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D37" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E37" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F37">
         <v>75</v>
@@ -5837,7 +5837,7 @@
         <v>55</v>
       </c>
       <c r="H37" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5845,16 +5845,16 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C38" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D38" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E38" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F38">
         <v>33</v>
@@ -5863,7 +5863,7 @@
         <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5871,16 +5871,16 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C39" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D39" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E39" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F39">
         <v>32</v>
@@ -5889,7 +5889,7 @@
         <v>22</v>
       </c>
       <c r="H39" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5897,16 +5897,16 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C40" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D40" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E40" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F40">
         <v>43</v>
@@ -5915,7 +5915,7 @@
         <v>29</v>
       </c>
       <c r="H40" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5923,16 +5923,16 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C41" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D41" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E41" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F41">
         <v>41</v>
@@ -5941,7 +5941,7 @@
         <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5949,16 +5949,16 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C42" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D42" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E42" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F42">
         <v>42</v>
@@ -5967,7 +5967,7 @@
         <v>26</v>
       </c>
       <c r="H42" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5975,16 +5975,16 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C43" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D43" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E43" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F43">
         <v>17</v>
@@ -5993,7 +5993,7 @@
         <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6001,16 +6001,16 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C44" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E44" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F44">
         <v>45</v>
@@ -6019,7 +6019,7 @@
         <v>32</v>
       </c>
       <c r="H44" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6027,16 +6027,16 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C45" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D45" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E45" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F45">
         <v>39</v>
@@ -6045,7 +6045,7 @@
         <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6053,16 +6053,16 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C46" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D46" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E46" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F46">
         <v>61</v>
@@ -6071,7 +6071,7 @@
         <v>38</v>
       </c>
       <c r="H46" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6079,16 +6079,16 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C47" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D47" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E47" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F47">
         <v>55</v>
@@ -6097,7 +6097,7 @@
         <v>39</v>
       </c>
       <c r="H47" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6105,16 +6105,16 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C48" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D48" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E48" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F48">
         <v>61</v>
@@ -6123,7 +6123,7 @@
         <v>32</v>
       </c>
       <c r="H48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6131,16 +6131,16 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C49" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D49" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E49" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F49">
         <v>54</v>
@@ -6149,7 +6149,7 @@
         <v>39</v>
       </c>
       <c r="H49" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6157,16 +6157,16 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
+        <v>508</v>
+      </c>
+      <c r="C50" t="s">
+        <v>587</v>
+      </c>
+      <c r="D50" t="s">
         <v>510</v>
       </c>
-      <c r="C50" t="s">
-        <v>589</v>
-      </c>
-      <c r="D50" t="s">
-        <v>512</v>
-      </c>
       <c r="E50" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -6175,7 +6175,7 @@
         <v>3</v>
       </c>
       <c r="H50" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6183,16 +6183,16 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C51" t="s">
+        <v>587</v>
+      </c>
+      <c r="D51" t="s">
         <v>589</v>
       </c>
-      <c r="D51" t="s">
-        <v>591</v>
-      </c>
       <c r="E51" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F51">
         <v>2</v>
@@ -6201,7 +6201,7 @@
         <v>3</v>
       </c>
       <c r="H51" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6209,16 +6209,16 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C52" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D52" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E52" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F52">
         <v>2</v>
@@ -6227,7 +6227,7 @@
         <v>3</v>
       </c>
       <c r="H52" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6235,25 +6235,25 @@
         <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C53" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D53" t="s">
+        <v>593</v>
+      </c>
+      <c r="E53" t="s">
+        <v>594</v>
+      </c>
+      <c r="F53" t="s">
         <v>595</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>596</v>
       </c>
-      <c r="F53" t="s">
-        <v>597</v>
-      </c>
-      <c r="G53" t="s">
-        <v>598</v>
-      </c>
       <c r="H53" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6261,25 +6261,25 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C54" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D54" t="s">
+        <v>597</v>
+      </c>
+      <c r="E54" t="s">
+        <v>598</v>
+      </c>
+      <c r="F54" t="s">
         <v>599</v>
       </c>
-      <c r="E54" t="s">
-        <v>600</v>
-      </c>
-      <c r="F54" t="s">
-        <v>601</v>
-      </c>
       <c r="G54" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H54" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6287,25 +6287,25 @@
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C55" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D55" t="s">
+        <v>600</v>
+      </c>
+      <c r="E55" t="s">
+        <v>601</v>
+      </c>
+      <c r="F55" t="s">
         <v>602</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>603</v>
       </c>
-      <c r="F55" t="s">
-        <v>604</v>
-      </c>
-      <c r="G55" t="s">
-        <v>605</v>
-      </c>
       <c r="H55" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6313,25 +6313,25 @@
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C56" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D56" t="s">
+        <v>604</v>
+      </c>
+      <c r="E56" t="s">
+        <v>605</v>
+      </c>
+      <c r="F56" t="s">
         <v>606</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>607</v>
       </c>
-      <c r="F56" t="s">
-        <v>608</v>
-      </c>
-      <c r="G56" t="s">
-        <v>609</v>
-      </c>
       <c r="H56" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6339,16 +6339,16 @@
         <v>18</v>
       </c>
       <c r="B57" t="s">
+        <v>492</v>
+      </c>
+      <c r="C57" t="s">
+        <v>608</v>
+      </c>
+      <c r="D57" t="s">
         <v>494</v>
       </c>
-      <c r="C57" t="s">
-        <v>610</v>
-      </c>
-      <c r="D57" t="s">
-        <v>496</v>
-      </c>
       <c r="E57" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F57">
         <v>53.7</v>
@@ -6357,7 +6357,7 @@
         <v>65.599999999999994</v>
       </c>
       <c r="H57" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6365,16 +6365,16 @@
         <v>18</v>
       </c>
       <c r="B58" t="s">
+        <v>501</v>
+      </c>
+      <c r="C58" t="s">
+        <v>610</v>
+      </c>
+      <c r="D58" t="s">
         <v>503</v>
       </c>
-      <c r="C58" t="s">
-        <v>612</v>
-      </c>
-      <c r="D58" t="s">
-        <v>505</v>
-      </c>
       <c r="E58" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F58">
         <v>0.52</v>
@@ -6383,7 +6383,7 @@
         <v>0.37</v>
       </c>
       <c r="H58" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6391,16 +6391,16 @@
         <v>18</v>
       </c>
       <c r="B59" t="s">
+        <v>508</v>
+      </c>
+      <c r="C59" t="s">
+        <v>612</v>
+      </c>
+      <c r="D59" t="s">
         <v>510</v>
       </c>
-      <c r="C59" t="s">
-        <v>614</v>
-      </c>
-      <c r="D59" t="s">
-        <v>512</v>
-      </c>
       <c r="E59" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F59">
         <v>0.31</v>
@@ -6409,7 +6409,7 @@
         <v>0.21</v>
       </c>
       <c r="H59" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6417,16 +6417,16 @@
         <v>18</v>
       </c>
       <c r="B60" t="s">
+        <v>614</v>
+      </c>
+      <c r="C60" t="s">
+        <v>615</v>
+      </c>
+      <c r="D60" t="s">
         <v>616</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>617</v>
-      </c>
-      <c r="D60" t="s">
-        <v>618</v>
-      </c>
-      <c r="E60" t="s">
-        <v>619</v>
       </c>
       <c r="F60">
         <v>62</v>
@@ -6435,7 +6435,7 @@
         <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6443,16 +6443,16 @@
         <v>18</v>
       </c>
       <c r="B61" t="s">
+        <v>618</v>
+      </c>
+      <c r="C61" t="s">
+        <v>619</v>
+      </c>
+      <c r="D61" t="s">
         <v>620</v>
       </c>
-      <c r="C61" t="s">
+      <c r="E61" t="s">
         <v>621</v>
-      </c>
-      <c r="D61" t="s">
-        <v>622</v>
-      </c>
-      <c r="E61" t="s">
-        <v>623</v>
       </c>
       <c r="F61">
         <v>49</v>
@@ -6461,7 +6461,7 @@
         <v>100</v>
       </c>
       <c r="H61" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6469,16 +6469,16 @@
         <v>18</v>
       </c>
       <c r="B62" t="s">
+        <v>622</v>
+      </c>
+      <c r="C62" t="s">
+        <v>623</v>
+      </c>
+      <c r="D62" t="s">
         <v>624</v>
       </c>
-      <c r="C62" t="s">
+      <c r="E62" t="s">
         <v>625</v>
-      </c>
-      <c r="D62" t="s">
-        <v>626</v>
-      </c>
-      <c r="E62" t="s">
-        <v>627</v>
       </c>
       <c r="F62">
         <v>7</v>
@@ -6487,7 +6487,7 @@
         <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6495,16 +6495,16 @@
         <v>29</v>
       </c>
       <c r="B63" t="s">
+        <v>492</v>
+      </c>
+      <c r="C63" t="s">
+        <v>626</v>
+      </c>
+      <c r="D63" t="s">
         <v>494</v>
       </c>
-      <c r="C63" t="s">
-        <v>628</v>
-      </c>
-      <c r="D63" t="s">
-        <v>496</v>
-      </c>
       <c r="E63" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F63">
         <v>19.25</v>
@@ -6513,7 +6513,7 @@
         <v>17.329999999999998</v>
       </c>
       <c r="H63" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6521,16 +6521,16 @@
         <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C64" t="s">
+        <v>626</v>
+      </c>
+      <c r="D64" t="s">
+        <v>497</v>
+      </c>
+      <c r="E64" t="s">
         <v>628</v>
-      </c>
-      <c r="D64" t="s">
-        <v>499</v>
-      </c>
-      <c r="E64" t="s">
-        <v>630</v>
       </c>
       <c r="F64">
         <v>823.74</v>
@@ -6539,7 +6539,7 @@
         <v>741.37</v>
       </c>
       <c r="H64" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6547,16 +6547,16 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" t="s">
+        <v>629</v>
+      </c>
+      <c r="D65" t="s">
         <v>503</v>
       </c>
-      <c r="C65" t="s">
-        <v>631</v>
-      </c>
-      <c r="D65" t="s">
-        <v>505</v>
-      </c>
       <c r="E65" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F65">
         <v>7.2</v>
@@ -6565,7 +6565,7 @@
         <v>3.5</v>
       </c>
       <c r="H65" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6573,16 +6573,16 @@
         <v>29</v>
       </c>
       <c r="B66" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C66" t="s">
+        <v>629</v>
+      </c>
+      <c r="D66" t="s">
+        <v>506</v>
+      </c>
+      <c r="E66" t="s">
         <v>631</v>
-      </c>
-      <c r="D66" t="s">
-        <v>508</v>
-      </c>
-      <c r="E66" t="s">
-        <v>633</v>
       </c>
       <c r="F66">
         <v>8.27</v>
@@ -6591,7 +6591,7 @@
         <v>4.55</v>
       </c>
       <c r="H66" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6602,13 +6602,13 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D67" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E67" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -6617,7 +6617,7 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6628,13 +6628,13 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
+        <v>632</v>
+      </c>
+      <c r="D68" t="s">
+        <v>497</v>
+      </c>
+      <c r="E68" t="s">
         <v>634</v>
-      </c>
-      <c r="D68" t="s">
-        <v>499</v>
-      </c>
-      <c r="E68" t="s">
-        <v>636</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -6643,7 +6643,7 @@
         <v>70</v>
       </c>
       <c r="H68" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6654,13 +6654,13 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D69" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E69" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>60</v>
       </c>
       <c r="H69" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6680,13 +6680,13 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D70" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E70" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -6695,7 +6695,7 @@
         <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6706,13 +6706,13 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
+        <v>636</v>
+      </c>
+      <c r="D71" t="s">
+        <v>506</v>
+      </c>
+      <c r="E71" t="s">
         <v>638</v>
-      </c>
-      <c r="D71" t="s">
-        <v>508</v>
-      </c>
-      <c r="E71" t="s">
-        <v>640</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -6721,7 +6721,7 @@
         <v>45</v>
       </c>
       <c r="H71" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6732,13 +6732,13 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D72" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E72" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>80</v>
       </c>
       <c r="H72" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -6758,13 +6758,13 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D73" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E73" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>11</v>
       </c>
       <c r="H73" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
@@ -6784,13 +6784,13 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D74" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E74" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -6799,7 +6799,7 @@
         <v>70</v>
       </c>
       <c r="H74" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -6810,13 +6810,13 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D75" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E75" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -6825,7 +6825,7 @@
         <v>60</v>
       </c>
       <c r="H75" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
@@ -6836,13 +6836,13 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D76" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E76" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -6851,7 +6851,7 @@
         <v>70</v>
       </c>
       <c r="H76" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
@@ -6862,13 +6862,13 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
+        <v>643</v>
+      </c>
+      <c r="D77" t="s">
+        <v>589</v>
+      </c>
+      <c r="E77" t="s">
         <v>645</v>
-      </c>
-      <c r="D77" t="s">
-        <v>591</v>
-      </c>
-      <c r="E77" t="s">
-        <v>647</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -6888,13 +6888,13 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D78" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E78" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>75</v>
       </c>
       <c r="H78" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
@@ -6914,22 +6914,22 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
+        <v>647</v>
+      </c>
+      <c r="D79" t="s">
+        <v>494</v>
+      </c>
+      <c r="E79" t="s">
+        <v>648</v>
+      </c>
+      <c r="F79" t="s">
         <v>649</v>
       </c>
-      <c r="D79" t="s">
+      <c r="G79" t="s">
+        <v>649</v>
+      </c>
+      <c r="H79" t="s">
         <v>496</v>
-      </c>
-      <c r="E79" t="s">
-        <v>650</v>
-      </c>
-      <c r="F79" t="s">
-        <v>651</v>
-      </c>
-      <c r="G79" t="s">
-        <v>651</v>
-      </c>
-      <c r="H79" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
@@ -6940,22 +6940,22 @@
         <v>1</v>
       </c>
       <c r="C80" t="s">
+        <v>647</v>
+      </c>
+      <c r="D80" t="s">
+        <v>497</v>
+      </c>
+      <c r="E80" t="s">
+        <v>650</v>
+      </c>
+      <c r="F80" t="s">
         <v>649</v>
       </c>
-      <c r="D80" t="s">
-        <v>499</v>
-      </c>
-      <c r="E80" t="s">
-        <v>652</v>
-      </c>
-      <c r="F80" t="s">
-        <v>651</v>
-      </c>
       <c r="G80" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H80" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
@@ -6966,22 +6966,22 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
+        <v>647</v>
+      </c>
+      <c r="D81" t="s">
+        <v>499</v>
+      </c>
+      <c r="E81" t="s">
+        <v>651</v>
+      </c>
+      <c r="F81" t="s">
         <v>649</v>
       </c>
-      <c r="D81" t="s">
-        <v>501</v>
-      </c>
-      <c r="E81" t="s">
-        <v>653</v>
-      </c>
-      <c r="F81" t="s">
-        <v>651</v>
-      </c>
       <c r="G81" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H81" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
@@ -6992,22 +6992,22 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
+        <v>647</v>
+      </c>
+      <c r="D82" t="s">
+        <v>517</v>
+      </c>
+      <c r="E82" t="s">
+        <v>652</v>
+      </c>
+      <c r="F82" t="s">
         <v>649</v>
       </c>
-      <c r="D82" t="s">
-        <v>519</v>
-      </c>
-      <c r="E82" t="s">
-        <v>654</v>
-      </c>
-      <c r="F82" t="s">
-        <v>651</v>
-      </c>
       <c r="G82" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H82" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
@@ -7018,22 +7018,22 @@
         <v>5</v>
       </c>
       <c r="C83" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D83" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E83" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F83" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G83" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H83" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -7044,22 +7044,22 @@
         <v>5</v>
       </c>
       <c r="C84" t="s">
+        <v>653</v>
+      </c>
+      <c r="D84" t="s">
         <v>655</v>
       </c>
-      <c r="D84" t="s">
-        <v>657</v>
-      </c>
       <c r="E84" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F84" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G84" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H84" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
@@ -7070,22 +7070,22 @@
         <v>5</v>
       </c>
       <c r="C85" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D85" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E85" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F85" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G85" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H85" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
@@ -7096,22 +7096,22 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D86" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E86" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F86" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G86" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H86" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
@@ -7122,22 +7122,22 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D87" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E87" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F87" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G87" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H87" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
@@ -7148,22 +7148,22 @@
         <v>6</v>
       </c>
       <c r="C88" t="s">
+        <v>661</v>
+      </c>
+      <c r="D88" t="s">
         <v>663</v>
       </c>
-      <c r="D88" t="s">
-        <v>665</v>
-      </c>
       <c r="E88" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F88" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G88" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H88" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
@@ -7174,22 +7174,22 @@
         <v>6</v>
       </c>
       <c r="C89" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D89" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E89" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F89" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G89" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H89" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -7200,22 +7200,22 @@
         <v>6</v>
       </c>
       <c r="C90" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D90" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E90" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F90" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G90" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H90" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -7226,22 +7226,22 @@
         <v>6</v>
       </c>
       <c r="C91" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D91" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E91" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F91" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G91" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H91" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -7252,22 +7252,22 @@
         <v>6</v>
       </c>
       <c r="C92" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D92" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E92" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F92" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G92" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H92" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -7278,13 +7278,13 @@
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D93" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E93" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F93">
         <v>102</v>
@@ -7293,7 +7293,7 @@
         <v>36</v>
       </c>
       <c r="H93" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
@@ -7304,13 +7304,13 @@
         <v>1</v>
       </c>
       <c r="C94" t="s">
+        <v>673</v>
+      </c>
+      <c r="D94" t="s">
+        <v>497</v>
+      </c>
+      <c r="E94" t="s">
         <v>675</v>
-      </c>
-      <c r="D94" t="s">
-        <v>499</v>
-      </c>
-      <c r="E94" t="s">
-        <v>677</v>
       </c>
       <c r="F94">
         <v>126</v>
@@ -7319,7 +7319,7 @@
         <v>45</v>
       </c>
       <c r="H94" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -7330,13 +7330,13 @@
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D95" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E95" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F95">
         <v>27.17</v>
@@ -7345,7 +7345,7 @@
         <v>22.66</v>
       </c>
       <c r="H95" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -7356,13 +7356,13 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D96" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E96" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F96">
         <v>63.6</v>
@@ -7371,7 +7371,7 @@
         <v>53.05</v>
       </c>
       <c r="H96" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -7382,13 +7382,13 @@
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D97" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E97" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F97">
         <v>66.069999999999993</v>
@@ -7397,7 +7397,7 @@
         <v>56.11</v>
       </c>
       <c r="H97" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
@@ -7408,13 +7408,13 @@
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D98" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E98" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F98">
         <v>2</v>
@@ -7423,7 +7423,7 @@
         <v>3</v>
       </c>
       <c r="H98" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -7434,13 +7434,13 @@
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D99" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E99" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F99">
         <v>3</v>
@@ -7449,7 +7449,7 @@
         <v>6</v>
       </c>
       <c r="H99" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
@@ -7460,13 +7460,13 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D100" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E100" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F100">
         <v>30</v>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="H100" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
@@ -7483,16 +7483,16 @@
         <v>33</v>
       </c>
       <c r="B101" t="s">
+        <v>492</v>
+      </c>
+      <c r="C101" t="s">
+        <v>682</v>
+      </c>
+      <c r="D101" t="s">
         <v>494</v>
       </c>
-      <c r="C101" t="s">
-        <v>684</v>
-      </c>
-      <c r="D101" t="s">
-        <v>496</v>
-      </c>
       <c r="E101" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F101">
         <v>39.07</v>
@@ -7501,7 +7501,7 @@
         <v>34.76</v>
       </c>
       <c r="H101" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -7509,16 +7509,16 @@
         <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C102" t="s">
+        <v>682</v>
+      </c>
+      <c r="D102" t="s">
+        <v>497</v>
+      </c>
+      <c r="E102" t="s">
         <v>684</v>
-      </c>
-      <c r="D102" t="s">
-        <v>499</v>
-      </c>
-      <c r="E102" t="s">
-        <v>686</v>
       </c>
       <c r="F102">
         <v>24.05</v>
@@ -7527,7 +7527,7 @@
         <v>11.93</v>
       </c>
       <c r="H102" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -7535,16 +7535,16 @@
         <v>33</v>
       </c>
       <c r="B103" t="s">
+        <v>501</v>
+      </c>
+      <c r="C103" t="s">
+        <v>685</v>
+      </c>
+      <c r="D103" t="s">
         <v>503</v>
       </c>
-      <c r="C103" t="s">
-        <v>687</v>
-      </c>
-      <c r="D103" t="s">
-        <v>505</v>
-      </c>
       <c r="E103" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F103">
         <v>75.599999999999994</v>
@@ -7553,7 +7553,7 @@
         <v>56.1</v>
       </c>
       <c r="H103" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
@@ -7561,16 +7561,16 @@
         <v>33</v>
       </c>
       <c r="B104" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C104" t="s">
+        <v>685</v>
+      </c>
+      <c r="D104" t="s">
+        <v>506</v>
+      </c>
+      <c r="E104" t="s">
         <v>687</v>
-      </c>
-      <c r="D104" t="s">
-        <v>508</v>
-      </c>
-      <c r="E104" t="s">
-        <v>689</v>
       </c>
       <c r="F104">
         <v>10.8</v>
@@ -7579,7 +7579,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H104" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
@@ -7587,16 +7587,16 @@
         <v>33</v>
       </c>
       <c r="B105" t="s">
+        <v>508</v>
+      </c>
+      <c r="C105" t="s">
+        <v>688</v>
+      </c>
+      <c r="D105" t="s">
         <v>510</v>
       </c>
-      <c r="C105" t="s">
-        <v>690</v>
-      </c>
-      <c r="D105" t="s">
-        <v>512</v>
-      </c>
       <c r="E105" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>11449</v>
       </c>
       <c r="H105" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
@@ -7613,16 +7613,16 @@
         <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C106" t="s">
+        <v>688</v>
+      </c>
+      <c r="D106" t="s">
+        <v>589</v>
+      </c>
+      <c r="E106" t="s">
         <v>690</v>
-      </c>
-      <c r="D106" t="s">
-        <v>591</v>
-      </c>
-      <c r="E106" t="s">
-        <v>692</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -7631,7 +7631,7 @@
         <v>3820</v>
       </c>
       <c r="H106" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7639,16 +7639,16 @@
         <v>33</v>
       </c>
       <c r="B107" t="s">
+        <v>614</v>
+      </c>
+      <c r="C107" t="s">
+        <v>691</v>
+      </c>
+      <c r="D107" t="s">
         <v>616</v>
       </c>
-      <c r="C107" t="s">
-        <v>693</v>
-      </c>
-      <c r="D107" t="s">
-        <v>618</v>
-      </c>
       <c r="E107" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -7657,7 +7657,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7692,24 +7692,24 @@
   <sheetData>
     <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>347</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7717,10 +7717,10 @@
         <v>29</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7728,10 +7728,10 @@
         <v>29</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7739,13 +7739,13 @@
         <v>29</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D6" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>353</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7753,13 +7753,13 @@
         <v>29</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7767,10 +7767,10 @@
         <v>29</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7778,10 +7778,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -7789,13 +7789,13 @@
         <v>29</v>
       </c>
       <c r="C10" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>360</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7803,10 +7803,10 @@
         <v>29</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7814,16 +7814,16 @@
         <v>24</v>
       </c>
       <c r="C12" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>364</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7831,13 +7831,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7845,13 +7845,13 @@
         <v>24</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7859,13 +7859,13 @@
         <v>24</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7873,13 +7873,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7887,13 +7887,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7901,10 +7901,10 @@
         <v>24</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
@@ -7914,13 +7914,13 @@
         <v>64</v>
       </c>
       <c r="C19" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>378</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7928,13 +7928,13 @@
         <v>64</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7942,13 +7942,13 @@
         <v>64</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7956,13 +7956,13 @@
         <v>64</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7970,10 +7970,10 @@
         <v>64</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -7983,10 +7983,10 @@
         <v>64</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -7996,10 +7996,10 @@
         <v>64</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
@@ -8009,10 +8009,10 @@
         <v>64</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
@@ -8022,13 +8022,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
@@ -8036,10 +8036,10 @@
         <v>18</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E28" s="20"/>
     </row>
@@ -8048,10 +8048,10 @@
         <v>18</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E29" s="20"/>
     </row>
@@ -8060,10 +8060,10 @@
         <v>18</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E30" s="20"/>
     </row>
@@ -8072,10 +8072,10 @@
         <v>18</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E31" s="20"/>
     </row>
@@ -8084,10 +8084,10 @@
         <v>18</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E32" s="20"/>
     </row>
@@ -8096,16 +8096,16 @@
         <v>18</v>
       </c>
       <c r="C33" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="F33" s="18" t="s">
         <v>397</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8113,16 +8113,16 @@
         <v>18</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -8130,13 +8130,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F35" s="23"/>
     </row>
@@ -8145,13 +8145,13 @@
         <v>33</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F36"/>
     </row>
@@ -8160,10 +8160,10 @@
         <v>33</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="15"/>
@@ -8173,10 +8173,10 @@
         <v>33</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="15"/>
@@ -8186,13 +8186,13 @@
         <v>33</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
@@ -8200,10 +8200,10 @@
         <v>33</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
@@ -8213,16 +8213,16 @@
         <v>85</v>
       </c>
       <c r="C41" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="F41" s="18" t="s">
         <v>411</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8230,13 +8230,13 @@
         <v>85</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -8244,13 +8244,13 @@
         <v>85</v>
       </c>
       <c r="C43" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E43" s="20" t="s">
         <v>414</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -8258,13 +8258,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
@@ -8272,13 +8272,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -8286,13 +8286,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8300,10 +8300,10 @@
         <v>6</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8311,10 +8311,10 @@
         <v>6</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8322,10 +8322,10 @@
         <v>21</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E49" s="21"/>
       <c r="F49" s="21"/>
@@ -8335,10 +8335,10 @@
         <v>21</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E50" s="21"/>
       <c r="F50" s="21"/>
@@ -8348,10 +8348,10 @@
         <v>21</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E51" s="21"/>
       <c r="F51" s="21"/>
@@ -8361,10 +8361,10 @@
         <v>21</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
@@ -8374,10 +8374,10 @@
         <v>21</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
@@ -8387,10 +8387,10 @@
         <v>21</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E54" s="21"/>
       <c r="F54" s="21"/>
@@ -8400,10 +8400,10 @@
         <v>21</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
@@ -8413,10 +8413,10 @@
         <v>21</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E56" s="21"/>
       <c r="F56" s="21"/>
@@ -8426,10 +8426,10 @@
         <v>21</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
@@ -8439,10 +8439,10 @@
         <v>21</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
@@ -8452,10 +8452,10 @@
         <v>21</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
@@ -8465,10 +8465,10 @@
         <v>21</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="21"/>
@@ -8478,10 +8478,10 @@
         <v>21</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
@@ -8491,10 +8491,10 @@
         <v>70</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
@@ -8504,10 +8504,10 @@
         <v>70</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
@@ -8517,10 +8517,10 @@
         <v>70</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
@@ -8530,10 +8530,10 @@
         <v>70</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
@@ -8543,10 +8543,10 @@
         <v>70</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
@@ -8556,10 +8556,10 @@
         <v>70</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
@@ -8569,10 +8569,10 @@
         <v>14</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
@@ -8582,10 +8582,10 @@
         <v>14</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
@@ -8595,10 +8595,10 @@
         <v>14</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
@@ -8608,10 +8608,10 @@
         <v>14</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
@@ -8632,22 +8632,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>695</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="A1" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8655,10 +8655,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8666,10 +8666,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8677,10 +8677,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8688,10 +8688,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8699,10 +8699,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8710,10 +8710,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8721,10 +8721,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8732,10 +8732,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8743,10 +8743,10 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8754,10 +8754,10 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8765,10 +8765,10 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8776,10 +8776,10 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8787,10 +8787,10 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C16" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8798,10 +8798,10 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C17" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8809,10 +8809,10 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8820,10 +8820,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C19" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8831,10 +8831,10 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C20" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8842,10 +8842,10 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8853,10 +8853,10 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8864,10 +8864,10 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C23" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8875,10 +8875,10 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C24" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8886,10 +8886,10 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C25" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8897,10 +8897,10 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C26" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8908,10 +8908,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C27" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8919,10 +8919,10 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8930,10 +8930,10 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8941,10 +8941,10 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C30" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8952,10 +8952,10 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C31" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8963,10 +8963,10 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C32" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8974,10 +8974,10 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C33" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8985,10 +8985,10 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C34" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8996,10 +8996,10 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C35" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9007,10 +9007,10 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C36" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9018,10 +9018,10 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C37" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9029,10 +9029,10 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C38" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9040,10 +9040,10 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C39" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9051,10 +9051,10 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C40" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9062,10 +9062,10 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9073,10 +9073,10 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C42" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9084,10 +9084,10 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C43" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9095,10 +9095,10 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C44" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9106,10 +9106,10 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C45" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9117,10 +9117,10 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C46" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9128,10 +9128,10 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C47" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9139,10 +9139,10 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C48" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9150,10 +9150,10 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C49" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9161,10 +9161,10 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9172,10 +9172,10 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C51" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9183,10 +9183,10 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C52" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9194,10 +9194,10 @@
         <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C53" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9205,10 +9205,10 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C54" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9216,10 +9216,10 @@
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C55" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9227,10 +9227,10 @@
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C56" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9238,10 +9238,10 @@
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C57" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9249,10 +9249,10 @@
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C58" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9260,10 +9260,10 @@
         <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C59" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9271,10 +9271,10 @@
         <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C60" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9282,10 +9282,10 @@
         <v>6</v>
       </c>
       <c r="B61" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C61" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9293,10 +9293,10 @@
         <v>6</v>
       </c>
       <c r="B62" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C62" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9304,10 +9304,10 @@
         <v>6</v>
       </c>
       <c r="B63" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C63" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9315,10 +9315,10 @@
         <v>6</v>
       </c>
       <c r="B64" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C64" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9326,10 +9326,10 @@
         <v>6</v>
       </c>
       <c r="B65" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C65" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9337,10 +9337,10 @@
         <v>18</v>
       </c>
       <c r="B66" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9348,10 +9348,10 @@
         <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C67" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9359,10 +9359,10 @@
         <v>18</v>
       </c>
       <c r="B68" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C68" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9370,10 +9370,10 @@
         <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C69" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9381,10 +9381,10 @@
         <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C70" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9392,10 +9392,10 @@
         <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C71" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9403,10 +9403,10 @@
         <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C72" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9414,10 +9414,10 @@
         <v>18</v>
       </c>
       <c r="B73" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C73" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9425,10 +9425,10 @@
         <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C74" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9436,10 +9436,10 @@
         <v>18</v>
       </c>
       <c r="B75" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C75" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9447,10 +9447,10 @@
         <v>18</v>
       </c>
       <c r="B76" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C76" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9458,10 +9458,10 @@
         <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C77" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9469,10 +9469,10 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C78" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9480,10 +9480,10 @@
         <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C79" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9491,10 +9491,10 @@
         <v>29</v>
       </c>
       <c r="B80" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C80" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9502,10 +9502,10 @@
         <v>29</v>
       </c>
       <c r="B81" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C81" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9513,10 +9513,10 @@
         <v>29</v>
       </c>
       <c r="B82" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C82" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9524,10 +9524,10 @@
         <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C83" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9535,10 +9535,10 @@
         <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C84" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9546,10 +9546,10 @@
         <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C85" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9557,10 +9557,10 @@
         <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C86" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9568,10 +9568,10 @@
         <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C87" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9579,10 +9579,10 @@
         <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C88" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9590,10 +9590,10 @@
         <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C89" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9601,10 +9601,10 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C90" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9612,10 +9612,10 @@
         <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C91" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9623,10 +9623,10 @@
         <v>29</v>
       </c>
       <c r="B92" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C92" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9634,10 +9634,10 @@
         <v>21</v>
       </c>
       <c r="B93" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C93" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9645,10 +9645,10 @@
         <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C94" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9656,10 +9656,10 @@
         <v>21</v>
       </c>
       <c r="B95" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C95" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9667,10 +9667,10 @@
         <v>21</v>
       </c>
       <c r="B96" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C96" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9678,10 +9678,10 @@
         <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C97" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9689,10 +9689,10 @@
         <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C98" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9700,10 +9700,10 @@
         <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C99" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -9711,10 +9711,10 @@
         <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C100" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -9722,10 +9722,10 @@
         <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C101" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -9733,10 +9733,10 @@
         <v>21</v>
       </c>
       <c r="B102" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C102" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -9744,10 +9744,10 @@
         <v>21</v>
       </c>
       <c r="B103" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C103" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -9755,10 +9755,10 @@
         <v>21</v>
       </c>
       <c r="B104" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C104" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -9766,10 +9766,10 @@
         <v>21</v>
       </c>
       <c r="B105" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C105" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -9777,10 +9777,10 @@
         <v>21</v>
       </c>
       <c r="B106" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C106" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -9788,10 +9788,10 @@
         <v>70</v>
       </c>
       <c r="B107" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C107" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -9799,10 +9799,10 @@
         <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C108" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -9810,10 +9810,10 @@
         <v>70</v>
       </c>
       <c r="B109" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C109" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -9821,10 +9821,10 @@
         <v>70</v>
       </c>
       <c r="B110" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C110" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -9832,10 +9832,10 @@
         <v>70</v>
       </c>
       <c r="B111" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C111" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -9843,10 +9843,10 @@
         <v>70</v>
       </c>
       <c r="B112" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C112" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -9854,10 +9854,10 @@
         <v>70</v>
       </c>
       <c r="B113" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C113" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>70</v>
       </c>
       <c r="B114" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C114" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -9876,10 +9876,10 @@
         <v>70</v>
       </c>
       <c r="B115" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C115" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -9887,10 +9887,10 @@
         <v>70</v>
       </c>
       <c r="B116" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C116" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -9898,10 +9898,10 @@
         <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C117" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -9909,10 +9909,10 @@
         <v>70</v>
       </c>
       <c r="B118" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C118" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -9920,10 +9920,10 @@
         <v>70</v>
       </c>
       <c r="B119" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C119" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -9931,10 +9931,10 @@
         <v>70</v>
       </c>
       <c r="B120" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C120" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -9942,10 +9942,10 @@
         <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C121" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -9953,10 +9953,10 @@
         <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C122" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -9964,10 +9964,10 @@
         <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C123" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -9975,10 +9975,10 @@
         <v>70</v>
       </c>
       <c r="B124" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C124" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -9986,10 +9986,10 @@
         <v>70</v>
       </c>
       <c r="B125" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C125" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -9997,10 +9997,10 @@
         <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C126" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -10008,10 +10008,10 @@
         <v>70</v>
       </c>
       <c r="B127" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C127" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -10019,10 +10019,10 @@
         <v>70</v>
       </c>
       <c r="B128" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C128" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -10030,10 +10030,10 @@
         <v>64</v>
       </c>
       <c r="B129" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C129" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -10041,10 +10041,10 @@
         <v>64</v>
       </c>
       <c r="B130" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C130" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -10052,10 +10052,10 @@
         <v>64</v>
       </c>
       <c r="B131" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C131" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -10063,10 +10063,10 @@
         <v>64</v>
       </c>
       <c r="B132" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C132" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -10074,10 +10074,10 @@
         <v>64</v>
       </c>
       <c r="B133" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C133" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -10085,10 +10085,10 @@
         <v>64</v>
       </c>
       <c r="B134" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C134" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -10096,10 +10096,10 @@
         <v>64</v>
       </c>
       <c r="B135" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C135" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -10107,10 +10107,10 @@
         <v>64</v>
       </c>
       <c r="B136" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C136" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C137" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -10129,10 +10129,10 @@
         <v>64</v>
       </c>
       <c r="B138" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C138" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -10140,10 +10140,10 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C139" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -10151,10 +10151,10 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C140" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -10162,10 +10162,10 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C141" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -10173,10 +10173,10 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C142" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -10184,10 +10184,10 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C143" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -10195,10 +10195,10 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C144" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -10206,10 +10206,10 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C145" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -10217,10 +10217,10 @@
         <v>64</v>
       </c>
       <c r="B146" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C146" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -10228,10 +10228,10 @@
         <v>64</v>
       </c>
       <c r="B147" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C147" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -10239,10 +10239,10 @@
         <v>64</v>
       </c>
       <c r="B148" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C148" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -10250,10 +10250,10 @@
         <v>64</v>
       </c>
       <c r="B149" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C149" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -10261,10 +10261,10 @@
         <v>64</v>
       </c>
       <c r="B150" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C150" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
@@ -10272,10 +10272,10 @@
         <v>64</v>
       </c>
       <c r="B151" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C151" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -10283,10 +10283,10 @@
         <v>64</v>
       </c>
       <c r="B152" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C152" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -10294,10 +10294,10 @@
         <v>64</v>
       </c>
       <c r="B153" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C153" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -10305,10 +10305,10 @@
         <v>64</v>
       </c>
       <c r="B154" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C154" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -10316,10 +10316,10 @@
         <v>64</v>
       </c>
       <c r="B155" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C155" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -10327,10 +10327,10 @@
         <v>64</v>
       </c>
       <c r="B156" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C156" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
@@ -10338,10 +10338,10 @@
         <v>64</v>
       </c>
       <c r="B157" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C157" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -10349,10 +10349,10 @@
         <v>64</v>
       </c>
       <c r="B158" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C158" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -10360,10 +10360,10 @@
         <v>64</v>
       </c>
       <c r="B159" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C159" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>33</v>
       </c>
       <c r="B160" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C160" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
@@ -10382,10 +10382,10 @@
         <v>33</v>
       </c>
       <c r="B161" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C161" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -10393,10 +10393,10 @@
         <v>33</v>
       </c>
       <c r="B162" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -10404,10 +10404,10 @@
         <v>33</v>
       </c>
       <c r="B163" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -10415,10 +10415,10 @@
         <v>33</v>
       </c>
       <c r="B164" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C164" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -10426,10 +10426,10 @@
         <v>33</v>
       </c>
       <c r="B165" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C165" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -10437,10 +10437,10 @@
         <v>33</v>
       </c>
       <c r="B166" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C166" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10448,10 +10448,10 @@
         <v>33</v>
       </c>
       <c r="B167" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10459,10 +10459,10 @@
         <v>33</v>
       </c>
       <c r="B168" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10470,10 +10470,10 @@
         <v>33</v>
       </c>
       <c r="B169" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C169" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10481,10 +10481,10 @@
         <v>33</v>
       </c>
       <c r="B170" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C170" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10492,10 +10492,10 @@
         <v>33</v>
       </c>
       <c r="B171" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C171" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10503,10 +10503,10 @@
         <v>33</v>
       </c>
       <c r="B172" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10514,10 +10514,10 @@
         <v>33</v>
       </c>
       <c r="B173" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10525,10 +10525,10 @@
         <v>33</v>
       </c>
       <c r="B174" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C174" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10536,10 +10536,10 @@
         <v>33</v>
       </c>
       <c r="B175" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C175" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10571,29 +10571,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>702</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="A1" s="28" t="s">
+        <v>700</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
     </row>
     <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C3" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>703</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>704</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -10601,16 +10601,16 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C4" t="s">
+        <v>704</v>
+      </c>
+      <c r="D4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E4" t="s">
         <v>706</v>
-      </c>
-      <c r="D4" t="s">
-        <v>707</v>
-      </c>
-      <c r="E4" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -10618,13 +10618,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D5" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -10632,13 +10632,13 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -10646,16 +10646,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C7" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D7" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -10663,16 +10663,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C8" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D8" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E8" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -10680,13 +10680,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C9" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D9" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -10694,13 +10694,13 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C10" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D10" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -10708,16 +10708,16 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D11" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E11" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -10725,13 +10725,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D12" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -10739,13 +10739,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D13" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -10753,16 +10753,16 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C14" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D14" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E14" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -10770,13 +10770,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D15" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -10784,13 +10784,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C16" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D16" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -10798,13 +10798,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C17" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D17" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -10812,13 +10812,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C18" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -10826,13 +10826,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C19" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D19" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -10840,16 +10840,16 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C20" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D20" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E20" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -10857,13 +10857,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C21" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D21" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -10871,13 +10871,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C22" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D22" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -10885,13 +10885,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C23" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D23" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -10899,13 +10899,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C24" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D24" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -10913,13 +10913,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C25" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D25" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -10927,13 +10927,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C26" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -10941,13 +10941,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C27" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D27" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -10955,16 +10955,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C28" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D28" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E28" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -10972,13 +10972,13 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D29" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -10986,16 +10986,16 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C30" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D30" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E30" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -11003,13 +11003,13 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C31" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D31" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -11017,16 +11017,16 @@
         <v>33</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -11034,13 +11034,13 @@
         <v>33</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E33" s="15"/>
     </row>
@@ -11049,16 +11049,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -11066,13 +11066,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E35" s="15"/>
     </row>
@@ -11081,16 +11081,16 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C36" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D36" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E36" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -11098,16 +11098,16 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C37" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D37" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E37" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -11115,13 +11115,13 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C38" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D38" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -11129,16 +11129,16 @@
         <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C39" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D39" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E39" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -11146,16 +11146,16 @@
         <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C40" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D40" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E40" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -11163,16 +11163,16 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C41" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D41" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E41" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -11180,13 +11180,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C42" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D42" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -11194,13 +11194,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C43" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D43" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -11208,16 +11208,16 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C44" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D44" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E44" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -11225,16 +11225,16 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C45" t="s">
+        <v>803</v>
+      </c>
+      <c r="D45" t="s">
+        <v>705</v>
+      </c>
+      <c r="E45" t="s">
         <v>805</v>
-      </c>
-      <c r="D45" t="s">
-        <v>707</v>
-      </c>
-      <c r="E45" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -11242,16 +11242,16 @@
         <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C46" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D46" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E46" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -11259,16 +11259,16 @@
         <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C47" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D47" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E47" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -11276,16 +11276,16 @@
         <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C48" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D48" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E48" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -11293,16 +11293,16 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C49" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D49" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E49" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -11310,16 +11310,16 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C50" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D50" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E50" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -11327,16 +11327,16 @@
         <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D51" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E51" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -11344,13 +11344,13 @@
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C52" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D52" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -11358,13 +11358,13 @@
         <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D53" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -11372,13 +11372,13 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C54" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D54" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -11386,13 +11386,13 @@
         <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D55" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -11400,13 +11400,13 @@
         <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C56" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D56" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -11414,16 +11414,16 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C57" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D57" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E57" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -11431,16 +11431,16 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C58" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D58" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E58" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -11448,16 +11448,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C59" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D59" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E59" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -11465,13 +11465,13 @@
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C60" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D60" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -11479,13 +11479,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C61" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D61" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -11493,13 +11493,13 @@
         <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C62" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D62" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -11507,13 +11507,13 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C63" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D63" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -11521,13 +11521,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C64" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D64" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -11535,13 +11535,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C65" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D65" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -11549,13 +11549,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C66" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D66" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>
@@ -11580,93 +11580,93 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>777</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>778</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>779</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>780</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B2" s="12">
         <v>46184</v>
       </c>
       <c r="C2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B3" s="12">
         <v>46184</v>
       </c>
       <c r="C3" t="s">
+        <v>781</v>
+      </c>
+      <c r="D3" t="s">
+        <v>785</v>
+      </c>
+      <c r="E3" t="s">
         <v>783</v>
-      </c>
-      <c r="D3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E3" t="s">
-        <v>785</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B4" s="12">
         <v>46184</v>
       </c>
       <c r="C4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D4" t="s">
+        <v>787</v>
+      </c>
+      <c r="E4" t="s">
         <v>783</v>
-      </c>
-      <c r="D4" t="s">
-        <v>789</v>
-      </c>
-      <c r="E4" t="s">
-        <v>785</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B5" s="12">
         <v>46184</v>
       </c>
       <c r="C5" t="s">
+        <v>781</v>
+      </c>
+      <c r="D5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E5" t="s">
         <v>783</v>
-      </c>
-      <c r="D5" t="s">
-        <v>789</v>
-      </c>
-      <c r="E5" t="s">
-        <v>785</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -11678,13 +11678,13 @@
         <v>46185</v>
       </c>
       <c r="C6" t="s">
+        <v>781</v>
+      </c>
+      <c r="D6" t="s">
+        <v>789</v>
+      </c>
+      <c r="E6" t="s">
         <v>783</v>
-      </c>
-      <c r="D6" t="s">
-        <v>791</v>
-      </c>
-      <c r="E6" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -11695,13 +11695,13 @@
         <v>46273</v>
       </c>
       <c r="C7" t="s">
+        <v>781</v>
+      </c>
+      <c r="D7" t="s">
+        <v>799</v>
+      </c>
+      <c r="E7" t="s">
         <v>783</v>
-      </c>
-      <c r="D7" t="s">
-        <v>801</v>
-      </c>
-      <c r="E7" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -11712,13 +11712,13 @@
         <v>46273</v>
       </c>
       <c r="C8" t="s">
+        <v>781</v>
+      </c>
+      <c r="D8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E8" t="s">
         <v>783</v>
-      </c>
-      <c r="D8" t="s">
-        <v>800</v>
-      </c>
-      <c r="E8" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -11729,13 +11729,13 @@
         <v>46273</v>
       </c>
       <c r="C9" t="s">
+        <v>781</v>
+      </c>
+      <c r="D9" t="s">
+        <v>798</v>
+      </c>
+      <c r="E9" t="s">
         <v>783</v>
-      </c>
-      <c r="D9" t="s">
-        <v>800</v>
-      </c>
-      <c r="E9" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -11746,13 +11746,13 @@
         <v>46273</v>
       </c>
       <c r="C10" t="s">
+        <v>781</v>
+      </c>
+      <c r="D10" t="s">
+        <v>799</v>
+      </c>
+      <c r="E10" t="s">
         <v>783</v>
-      </c>
-      <c r="D10" t="s">
-        <v>801</v>
-      </c>
-      <c r="E10" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -11763,13 +11763,13 @@
         <v>46273</v>
       </c>
       <c r="C11" t="s">
+        <v>781</v>
+      </c>
+      <c r="D11" t="s">
+        <v>797</v>
+      </c>
+      <c r="E11" t="s">
         <v>783</v>
-      </c>
-      <c r="D11" t="s">
-        <v>799</v>
-      </c>
-      <c r="E11" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -11780,13 +11780,13 @@
         <v>46273</v>
       </c>
       <c r="C12" t="s">
+        <v>781</v>
+      </c>
+      <c r="D12" t="s">
+        <v>801</v>
+      </c>
+      <c r="E12" t="s">
         <v>783</v>
-      </c>
-      <c r="D12" t="s">
-        <v>803</v>
-      </c>
-      <c r="E12" t="s">
-        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -12957,7 +12957,7 @@
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
@@ -12971,7 +12971,7 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
@@ -12985,7 +12985,7 @@
         <v>33</v>
       </c>
       <c r="E85" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
@@ -12999,7 +12999,7 @@
         <v>64</v>
       </c>
       <c r="E86" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
@@ -13013,7 +13013,7 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B02447-C743-407D-8B91-E6031B2E34AF}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_4C9EC0392E1937393E1E0B6D50CE053FA31529A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E49D5CC9-B36A-41BC-90EC-50A1F7C7B4EC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2519" uniqueCount="812">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2392,9 +2392,6 @@
     <t>664364</t>
   </si>
   <si>
-    <t>Documentacion enviada por el ejecutor. En analisis por equipo de proyecto</t>
-  </si>
-  <si>
     <t>705320</t>
   </si>
   <si>
@@ -2468,6 +2465,12 @@
   </si>
   <si>
     <t>Plan financiero CR-L1137 sept 2026</t>
+  </si>
+  <si>
+    <t>Informe recibido en revisión</t>
+  </si>
+  <si>
+    <t>Documentacion enviada por el ejecutor. En proceso de registrar cumplimiento en convergencia.</t>
   </si>
 </sst>
 </file>
@@ -2710,7 +2713,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3047,17 +3050,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D79"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="8" customWidth="1"/>
     <col min="3" max="3" width="42" style="8" customWidth="1"/>
     <col min="4" max="4" width="80" style="8" customWidth="1"/>
-    <col min="5" max="15" width="8.88671875" style="8" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="8"/>
+    <col min="5" max="15" width="8.85546875" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>122</v>
       </c>
@@ -3065,8 +3068,8 @@
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -3080,7 +3083,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
@@ -3094,7 +3097,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
@@ -3108,7 +3111,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>131</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>29</v>
       </c>
@@ -3136,7 +3139,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>24</v>
       </c>
@@ -3164,7 +3167,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>64</v>
       </c>
@@ -3178,7 +3181,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
@@ -3192,7 +3195,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>85</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>6</v>
       </c>
@@ -3220,7 +3223,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>6</v>
       </c>
@@ -3234,7 +3237,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
@@ -3248,7 +3251,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>131</v>
       </c>
@@ -3262,7 +3265,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>29</v>
       </c>
@@ -3276,7 +3279,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>33</v>
       </c>
@@ -3290,7 +3293,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>24</v>
       </c>
@@ -3304,7 +3307,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>64</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>14</v>
       </c>
@@ -3332,7 +3335,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>85</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>6</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>6</v>
       </c>
@@ -3374,7 +3377,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>131</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>33</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>24</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>21</v>
       </c>
@@ -3444,7 +3447,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>14</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>6</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>14</v>
       </c>
@@ -3486,7 +3489,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
@@ -3500,7 +3503,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>6</v>
       </c>
@@ -3514,7 +3517,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>64</v>
       </c>
@@ -3528,7 +3531,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>18</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>29</v>
       </c>
@@ -3556,7 +3559,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>85</v>
       </c>
@@ -3564,13 +3567,13 @@
         <v>256</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D38" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>6</v>
       </c>
@@ -3584,7 +3587,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>18</v>
       </c>
@@ -3598,7 +3601,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>29</v>
       </c>
@@ -3606,13 +3609,13 @@
         <v>233</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>810</v>
-      </c>
-      <c r="D41" s="30" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>33</v>
       </c>
@@ -3626,7 +3629,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>64</v>
       </c>
@@ -3640,7 +3643,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>6</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>18</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>131</v>
       </c>
@@ -3682,7 +3685,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>29</v>
       </c>
@@ -3696,7 +3699,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>33</v>
       </c>
@@ -3710,7 +3713,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>24</v>
       </c>
@@ -3724,7 +3727,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>64</v>
       </c>
@@ -3738,7 +3741,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>14</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>14</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>6</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>131</v>
       </c>
@@ -3794,7 +3797,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>29</v>
       </c>
@@ -3808,7 +3811,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>33</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>24</v>
       </c>
@@ -3836,7 +3839,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>64</v>
       </c>
@@ -3850,7 +3853,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>21</v>
       </c>
@@ -3864,7 +3867,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>14</v>
       </c>
@@ -3878,7 +3881,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>24</v>
       </c>
@@ -3892,7 +3895,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>18</v>
       </c>
@@ -3906,7 +3909,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>33</v>
       </c>
@@ -3920,7 +3923,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>6</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>64</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>85</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>6</v>
       </c>
@@ -3976,7 +3979,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>131</v>
       </c>
@@ -3990,7 +3993,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>29</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>33</v>
       </c>
@@ -4018,7 +4021,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>6</v>
       </c>
@@ -4032,7 +4035,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>18</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>131</v>
       </c>
@@ -4060,7 +4063,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>29</v>
       </c>
@@ -4074,7 +4077,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>33</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>24</v>
       </c>
@@ -4102,7 +4105,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>64</v>
       </c>
@@ -4116,7 +4119,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>85</v>
       </c>
@@ -4130,7 +4133,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>85</v>
       </c>
@@ -4160,32 +4163,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="5">
         <v>46261</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>285</v>
       </c>
@@ -4220,7 +4223,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>286</v>
       </c>
@@ -4234,7 +4237,7 @@
         <v>288</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>287</v>
@@ -4255,7 +4258,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>294</v>
       </c>
@@ -4290,7 +4293,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>294</v>
       </c>
@@ -4302,7 +4305,7 @@
       </c>
       <c r="G8" s="4"/>
       <c r="H8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
@@ -4311,7 +4314,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>301</v>
       </c>
@@ -4344,7 +4347,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>306</v>
       </c>
@@ -4369,7 +4372,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>308</v>
       </c>
@@ -4404,7 +4407,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>310</v>
       </c>
@@ -4439,7 +4442,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>312</v>
       </c>
@@ -4474,7 +4477,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>315</v>
       </c>
@@ -4504,10 +4507,10 @@
         <v>319</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>315</v>
       </c>
@@ -4532,7 +4535,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>321</v>
       </c>
@@ -4567,7 +4570,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>328</v>
       </c>
@@ -4602,7 +4605,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>330</v>
       </c>
@@ -4635,7 +4638,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>334</v>
       </c>
@@ -4659,7 +4662,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>339</v>
       </c>
@@ -4679,7 +4682,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>341</v>
       </c>
@@ -4695,10 +4698,10 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C23" s="4"/>
     </row>
   </sheetData>
@@ -4709,14 +4712,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
-    <col min="5" max="5" width="44.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>446</v>
       </c>
@@ -4730,7 +4733,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>6</v>
       </c>
@@ -4744,7 +4747,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -4758,7 +4761,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>18</v>
       </c>
@@ -4772,7 +4775,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>33</v>
       </c>
@@ -4786,7 +4789,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>64</v>
       </c>
@@ -4800,7 +4803,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -4814,7 +4817,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>24</v>
       </c>
@@ -4828,7 +4831,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>131</v>
       </c>
@@ -4842,7 +4845,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>21</v>
       </c>
@@ -4856,7 +4859,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>70</v>
       </c>
@@ -4870,7 +4873,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -4884,7 +4887,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>85</v>
       </c>
@@ -4906,7 +4909,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4917,7 +4920,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>484</v>
       </c>
@@ -4929,8 +4932,8 @@
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
     </row>
-    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>343</v>
       </c>
@@ -4956,7 +4959,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4982,7 +4985,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5008,7 +5011,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -5034,7 +5037,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -5060,7 +5063,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5086,7 +5089,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -5138,7 +5141,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5164,7 +5167,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -5190,7 +5193,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -5216,7 +5219,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -5242,7 +5245,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5268,7 +5271,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -5294,7 +5297,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -5320,7 +5323,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -5346,7 +5349,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -5372,7 +5375,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -5398,7 +5401,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -5424,7 +5427,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -5450,7 +5453,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -5476,7 +5479,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -5502,7 +5505,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -5554,7 +5557,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -5580,7 +5583,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -5606,7 +5609,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -5632,7 +5635,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -5658,7 +5661,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -5684,7 +5687,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -5710,7 +5713,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -5736,7 +5739,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -5762,7 +5765,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -5788,7 +5791,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -5814,7 +5817,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -5840,7 +5843,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -5866,7 +5869,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -5892,7 +5895,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -5918,7 +5921,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -5944,7 +5947,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -5970,7 +5973,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -5996,7 +5999,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -6048,7 +6051,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -6074,7 +6077,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -6100,7 +6103,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -6126,7 +6129,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -6152,7 +6155,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -6178,7 +6181,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -6204,7 +6207,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -6230,7 +6233,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -6256,7 +6259,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -6334,7 +6337,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6360,7 +6363,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -6386,7 +6389,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -6412,7 +6415,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -6438,7 +6441,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -6464,7 +6467,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -6490,7 +6493,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>29</v>
       </c>
@@ -6516,7 +6519,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>29</v>
       </c>
@@ -6542,7 +6545,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -6568,7 +6571,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>29</v>
       </c>
@@ -6594,7 +6597,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -6620,7 +6623,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -6698,7 +6701,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -6724,7 +6727,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -6750,7 +6753,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -6776,7 +6779,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -6802,7 +6805,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -6828,7 +6831,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -6854,7 +6857,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -6880,7 +6883,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -6906,7 +6909,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>70</v>
       </c>
@@ -6932,7 +6935,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -6958,7 +6961,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>70</v>
       </c>
@@ -6984,7 +6987,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -7010,7 +7013,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>70</v>
       </c>
@@ -7036,7 +7039,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>70</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>70</v>
       </c>
@@ -7088,7 +7091,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>70</v>
       </c>
@@ -7114,7 +7117,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>70</v>
       </c>
@@ -7140,7 +7143,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>70</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>70</v>
       </c>
@@ -7192,7 +7195,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>70</v>
       </c>
@@ -7218,7 +7221,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>70</v>
       </c>
@@ -7244,7 +7247,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>70</v>
       </c>
@@ -7270,7 +7273,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>64</v>
       </c>
@@ -7296,7 +7299,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>64</v>
       </c>
@@ -7322,7 +7325,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>64</v>
       </c>
@@ -7348,7 +7351,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>64</v>
       </c>
@@ -7374,7 +7377,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>64</v>
       </c>
@@ -7400,7 +7403,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>64</v>
       </c>
@@ -7426,7 +7429,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>64</v>
       </c>
@@ -7452,7 +7455,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>64</v>
       </c>
@@ -7478,7 +7481,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -7504,7 +7507,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -7530,7 +7533,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -7556,7 +7559,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>33</v>
       </c>
@@ -7582,7 +7585,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -7608,7 +7611,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -7634,7 +7637,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -7660,12 +7663,12 @@
         <v>505</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:H113" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
@@ -7678,24 +7681,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:F71"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="18" customWidth="1"/>
     <col min="2" max="2" width="12" style="18" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="18" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="98.109375" style="18" customWidth="1"/>
-    <col min="7" max="18" width="8.88671875" style="18" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="18"/>
+    <col min="3" max="3" width="46.5703125" style="18" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="98.140625" style="18" customWidth="1"/>
+    <col min="7" max="18" width="8.85546875" style="18" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="18"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="19" t="s">
         <v>343</v>
       </c>
@@ -7712,7 +7715,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
         <v>29</v>
       </c>
@@ -7723,7 +7726,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="s">
         <v>29</v>
       </c>
@@ -7734,7 +7737,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18" t="s">
         <v>29</v>
       </c>
@@ -7748,7 +7751,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
         <v>29</v>
       </c>
@@ -7762,7 +7765,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
         <v>29</v>
       </c>
@@ -7773,7 +7776,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
         <v>29</v>
       </c>
@@ -7784,7 +7787,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="18" t="s">
         <v>29</v>
       </c>
@@ -7798,7 +7801,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="18" t="s">
         <v>29</v>
       </c>
@@ -7809,7 +7812,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="18" t="s">
         <v>24</v>
       </c>
@@ -7826,7 +7829,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
@@ -7840,7 +7843,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
         <v>24</v>
       </c>
@@ -7854,7 +7857,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
         <v>24</v>
       </c>
@@ -7868,7 +7871,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="18" t="s">
         <v>24</v>
       </c>
@@ -7882,7 +7885,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
         <v>24</v>
       </c>
@@ -7896,7 +7899,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="21" t="s">
         <v>24</v>
       </c>
@@ -7909,7 +7912,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
         <v>64</v>
       </c>
@@ -7923,7 +7926,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="s">
         <v>64</v>
       </c>
@@ -7937,7 +7940,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="s">
         <v>64</v>
       </c>
@@ -7951,7 +7954,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="s">
         <v>64</v>
       </c>
@@ -7965,7 +7968,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
         <v>64</v>
       </c>
@@ -7978,7 +7981,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
         <v>64</v>
       </c>
@@ -7991,7 +7994,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
         <v>64</v>
       </c>
@@ -8004,7 +8007,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
         <v>64</v>
       </c>
@@ -8017,7 +8020,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="s">
         <v>18</v>
       </c>
@@ -8031,7 +8034,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
         <v>18</v>
       </c>
@@ -8043,7 +8046,7 @@
       </c>
       <c r="E28" s="20"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="s">
         <v>18</v>
       </c>
@@ -8055,7 +8058,7 @@
       </c>
       <c r="E29" s="20"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="s">
         <v>18</v>
       </c>
@@ -8067,7 +8070,7 @@
       </c>
       <c r="E30" s="20"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="s">
         <v>18</v>
       </c>
@@ -8079,7 +8082,7 @@
       </c>
       <c r="E31" s="20"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="s">
         <v>18</v>
       </c>
@@ -8091,7 +8094,7 @@
       </c>
       <c r="E32" s="20"/>
     </row>
-    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="s">
         <v>18</v>
       </c>
@@ -8108,7 +8111,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="s">
         <v>18</v>
       </c>
@@ -8125,7 +8128,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="s">
         <v>33</v>
       </c>
@@ -8140,7 +8143,7 @@
       </c>
       <c r="F35" s="23"/>
     </row>
-    <row r="36" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="s">
         <v>33</v>
       </c>
@@ -8155,7 +8158,7 @@
       </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
         <v>33</v>
       </c>
@@ -8168,7 +8171,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="15"/>
     </row>
-    <row r="38" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="21" t="s">
         <v>33</v>
       </c>
@@ -8181,7 +8184,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="15"/>
     </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="s">
         <v>33</v>
       </c>
@@ -8195,7 +8198,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="21" t="s">
         <v>33</v>
       </c>
@@ -8208,7 +8211,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
@@ -8225,7 +8228,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="s">
         <v>85</v>
       </c>
@@ -8239,7 +8242,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="s">
         <v>85</v>
       </c>
@@ -8253,7 +8256,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="s">
         <v>6</v>
       </c>
@@ -8267,7 +8270,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="s">
         <v>6</v>
       </c>
@@ -8281,7 +8284,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="s">
         <v>6</v>
       </c>
@@ -8295,7 +8298,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="s">
         <v>6</v>
       </c>
@@ -8306,7 +8309,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="s">
         <v>6</v>
       </c>
@@ -8317,7 +8320,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
         <v>21</v>
       </c>
@@ -8330,7 +8333,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="21"/>
     </row>
-    <row r="50" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
         <v>21</v>
       </c>
@@ -8343,7 +8346,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="21"/>
     </row>
-    <row r="51" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
         <v>21</v>
       </c>
@@ -8356,7 +8359,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="21"/>
     </row>
-    <row r="52" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
         <v>21</v>
       </c>
@@ -8369,7 +8372,7 @@
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
     </row>
-    <row r="53" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
         <v>21</v>
       </c>
@@ -8382,7 +8385,7 @@
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
     </row>
-    <row r="54" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="21" t="s">
         <v>21</v>
       </c>
@@ -8395,7 +8398,7 @@
       <c r="E54" s="21"/>
       <c r="F54" s="21"/>
     </row>
-    <row r="55" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
         <v>21</v>
       </c>
@@ -8408,7 +8411,7 @@
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
     </row>
-    <row r="56" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="21" t="s">
         <v>21</v>
       </c>
@@ -8421,7 +8424,7 @@
       <c r="E56" s="21"/>
       <c r="F56" s="21"/>
     </row>
-    <row r="57" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
         <v>21</v>
       </c>
@@ -8434,7 +8437,7 @@
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
     </row>
-    <row r="58" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="21" t="s">
         <v>21</v>
       </c>
@@ -8447,7 +8450,7 @@
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
     </row>
-    <row r="59" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
         <v>21</v>
       </c>
@@ -8460,7 +8463,7 @@
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
     </row>
-    <row r="60" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
         <v>21</v>
       </c>
@@ -8473,7 +8476,7 @@
       <c r="E60" s="21"/>
       <c r="F60" s="21"/>
     </row>
-    <row r="61" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
         <v>21</v>
       </c>
@@ -8486,7 +8489,7 @@
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
     </row>
-    <row r="62" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
         <v>70</v>
       </c>
@@ -8499,7 +8502,7 @@
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
     </row>
-    <row r="63" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
         <v>70</v>
       </c>
@@ -8512,7 +8515,7 @@
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
     </row>
-    <row r="64" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
         <v>70</v>
       </c>
@@ -8525,7 +8528,7 @@
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
     </row>
-    <row r="65" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
         <v>70</v>
       </c>
@@ -8538,7 +8541,7 @@
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
     </row>
-    <row r="66" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
         <v>70</v>
       </c>
@@ -8551,7 +8554,7 @@
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
     </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
         <v>70</v>
       </c>
@@ -8564,7 +8567,7 @@
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
     </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
         <v>14</v>
       </c>
@@ -8577,7 +8580,7 @@
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
     </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
         <v>14</v>
       </c>
@@ -8590,7 +8593,7 @@
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
         <v>14</v>
       </c>
@@ -8603,7 +8606,7 @@
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
         <v>14</v>
       </c>
@@ -8625,21 +8628,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>693</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
     </row>
-    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>343</v>
       </c>
@@ -8650,7 +8653,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -8661,7 +8664,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -8672,7 +8675,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -8683,7 +8686,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -8694,7 +8697,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -8705,7 +8708,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -8716,7 +8719,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8727,7 +8730,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -8738,7 +8741,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -8749,7 +8752,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -8760,7 +8763,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -8771,7 +8774,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -8782,7 +8785,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -8793,7 +8796,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -8804,7 +8807,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -8815,7 +8818,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -8826,7 +8829,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -8837,7 +8840,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8848,7 +8851,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -8859,7 +8862,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -8870,7 +8873,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -8881,7 +8884,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -8892,7 +8895,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -8903,7 +8906,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -8914,7 +8917,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -8925,7 +8928,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -8936,7 +8939,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -8947,7 +8950,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -8958,7 +8961,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -8969,7 +8972,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -8980,7 +8983,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -8991,7 +8994,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -9002,7 +9005,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -9013,7 +9016,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -9024,7 +9027,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -9035,7 +9038,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -9046,7 +9049,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -9057,7 +9060,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -9068,7 +9071,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -9079,7 +9082,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -9090,7 +9093,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -9101,7 +9104,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -9112,7 +9115,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -9123,7 +9126,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -9134,7 +9137,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -9145,7 +9148,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -9156,7 +9159,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -9167,7 +9170,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -9178,7 +9181,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -9189,7 +9192,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -9200,7 +9203,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -9211,7 +9214,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -9222,7 +9225,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -9233,7 +9236,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -9244,7 +9247,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -9255,7 +9258,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -9266,7 +9269,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -9277,7 +9280,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -9288,7 +9291,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -9299,7 +9302,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -9310,7 +9313,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -9321,7 +9324,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -9332,7 +9335,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9343,7 +9346,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9354,7 +9357,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9365,7 +9368,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9376,7 +9379,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9387,7 +9390,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9398,7 +9401,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -9409,7 +9412,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9420,7 +9423,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -9431,7 +9434,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -9442,7 +9445,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -9453,7 +9456,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>29</v>
       </c>
@@ -9464,7 +9467,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>29</v>
       </c>
@@ -9475,7 +9478,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>29</v>
       </c>
@@ -9486,7 +9489,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -9497,7 +9500,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -9508,7 +9511,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>29</v>
       </c>
@@ -9519,7 +9522,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -9530,7 +9533,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>29</v>
       </c>
@@ -9541,7 +9544,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -9552,7 +9555,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -9563,7 +9566,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -9574,7 +9577,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -9585,7 +9588,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>29</v>
       </c>
@@ -9596,7 +9599,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>29</v>
       </c>
@@ -9607,7 +9610,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>29</v>
       </c>
@@ -9618,7 +9621,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -9629,7 +9632,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>21</v>
       </c>
@@ -9640,7 +9643,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -9651,7 +9654,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>21</v>
       </c>
@@ -9662,7 +9665,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>21</v>
       </c>
@@ -9673,7 +9676,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -9684,7 +9687,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>21</v>
       </c>
@@ -9695,7 +9698,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -9706,7 +9709,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>21</v>
       </c>
@@ -9717,7 +9720,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>21</v>
       </c>
@@ -9728,7 +9731,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -9739,7 +9742,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -9750,7 +9753,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>21</v>
       </c>
@@ -9761,7 +9764,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>21</v>
       </c>
@@ -9772,7 +9775,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>21</v>
       </c>
@@ -9783,7 +9786,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>70</v>
       </c>
@@ -9794,7 +9797,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>70</v>
       </c>
@@ -9805,7 +9808,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>70</v>
       </c>
@@ -9816,7 +9819,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>70</v>
       </c>
@@ -9827,7 +9830,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>70</v>
       </c>
@@ -9838,7 +9841,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>70</v>
       </c>
@@ -9849,7 +9852,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>70</v>
       </c>
@@ -9860,7 +9863,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>70</v>
       </c>
@@ -9871,7 +9874,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>70</v>
       </c>
@@ -9882,7 +9885,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>70</v>
       </c>
@@ -9893,7 +9896,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>70</v>
       </c>
@@ -9904,7 +9907,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>70</v>
       </c>
@@ -9915,7 +9918,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>70</v>
       </c>
@@ -9926,7 +9929,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>70</v>
       </c>
@@ -9937,7 +9940,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>70</v>
       </c>
@@ -9948,7 +9951,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>70</v>
       </c>
@@ -9959,7 +9962,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>70</v>
       </c>
@@ -9970,7 +9973,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>70</v>
       </c>
@@ -9981,7 +9984,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>70</v>
       </c>
@@ -9992,7 +9995,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>70</v>
       </c>
@@ -10003,7 +10006,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>70</v>
       </c>
@@ -10014,7 +10017,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -10025,7 +10028,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>64</v>
       </c>
@@ -10036,7 +10039,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>64</v>
       </c>
@@ -10047,7 +10050,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>64</v>
       </c>
@@ -10058,7 +10061,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>64</v>
       </c>
@@ -10069,7 +10072,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>64</v>
       </c>
@@ -10080,7 +10083,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>64</v>
       </c>
@@ -10091,7 +10094,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>64</v>
       </c>
@@ -10102,7 +10105,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>64</v>
       </c>
@@ -10113,7 +10116,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>64</v>
       </c>
@@ -10124,7 +10127,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>64</v>
       </c>
@@ -10135,7 +10138,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>64</v>
       </c>
@@ -10146,7 +10149,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>64</v>
       </c>
@@ -10157,7 +10160,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>64</v>
       </c>
@@ -10168,7 +10171,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>64</v>
       </c>
@@ -10179,7 +10182,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>64</v>
       </c>
@@ -10190,7 +10193,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>64</v>
       </c>
@@ -10201,7 +10204,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>64</v>
       </c>
@@ -10212,7 +10215,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>64</v>
       </c>
@@ -10223,7 +10226,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>64</v>
       </c>
@@ -10234,7 +10237,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>64</v>
       </c>
@@ -10245,7 +10248,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>64</v>
       </c>
@@ -10256,7 +10259,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>64</v>
       </c>
@@ -10267,7 +10270,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>64</v>
       </c>
@@ -10278,7 +10281,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>64</v>
       </c>
@@ -10289,7 +10292,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>64</v>
       </c>
@@ -10300,7 +10303,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>64</v>
       </c>
@@ -10311,7 +10314,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>64</v>
       </c>
@@ -10322,7 +10325,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>64</v>
       </c>
@@ -10333,7 +10336,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>64</v>
       </c>
@@ -10344,7 +10347,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>64</v>
       </c>
@@ -10355,7 +10358,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>64</v>
       </c>
@@ -10366,7 +10369,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>33</v>
       </c>
@@ -10377,7 +10380,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>33</v>
       </c>
@@ -10388,7 +10391,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>33</v>
       </c>
@@ -10399,7 +10402,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -10410,7 +10413,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>33</v>
       </c>
@@ -10421,7 +10424,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>33</v>
       </c>
@@ -10432,7 +10435,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>33</v>
       </c>
@@ -10443,7 +10446,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>33</v>
       </c>
@@ -10454,7 +10457,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>33</v>
       </c>
@@ -10465,7 +10468,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>33</v>
       </c>
@@ -10476,7 +10479,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>33</v>
       </c>
@@ -10487,7 +10490,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>33</v>
       </c>
@@ -10498,7 +10501,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>33</v>
       </c>
@@ -10509,7 +10512,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>33</v>
       </c>
@@ -10520,7 +10523,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>33</v>
       </c>
@@ -10531,7 +10534,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -10542,13 +10545,13 @@
         <v>406</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:C182" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="1">
@@ -10561,7 +10564,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E66"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10570,7 +10573,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>700</v>
       </c>
@@ -10579,7 +10582,7 @@
       <c r="D1" s="29"/>
       <c r="E1" s="29"/>
     </row>
-    <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>343</v>
       </c>
@@ -10596,7 +10599,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -10613,7 +10616,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -10627,7 +10630,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10641,7 +10644,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10658,7 +10661,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -10675,7 +10678,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -10689,7 +10692,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10703,7 +10706,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -10720,7 +10723,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -10734,7 +10737,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -10748,7 +10751,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -10765,7 +10768,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -10779,7 +10782,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -10793,7 +10796,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -10807,7 +10810,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -10821,7 +10824,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -10835,7 +10838,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -10852,7 +10855,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -10866,7 +10869,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -10880,7 +10883,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -10894,7 +10897,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -10908,7 +10911,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -10922,7 +10925,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -10936,7 +10939,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -10950,7 +10953,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -10967,7 +10970,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -10981,7 +10984,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -10998,7 +11001,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -11012,7 +11015,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>33</v>
       </c>
@@ -11029,7 +11032,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>33</v>
       </c>
@@ -11044,7 +11047,7 @@
       </c>
       <c r="E33" s="15"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>33</v>
       </c>
@@ -11061,7 +11064,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>33</v>
       </c>
@@ -11076,7 +11079,7 @@
       </c>
       <c r="E35" s="15"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -11093,7 +11096,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -11110,7 +11113,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -11124,7 +11127,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -11141,7 +11144,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -11158,7 +11161,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -11175,7 +11178,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -11189,7 +11192,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -11203,7 +11206,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -11211,16 +11214,16 @@
         <v>358</v>
       </c>
       <c r="C44" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D44" t="s">
         <v>705</v>
       </c>
       <c r="E44" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -11228,16 +11231,16 @@
         <v>358</v>
       </c>
       <c r="C45" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D45" t="s">
         <v>705</v>
       </c>
       <c r="E45" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -11245,16 +11248,16 @@
         <v>358</v>
       </c>
       <c r="C46" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D46" t="s">
         <v>705</v>
       </c>
       <c r="E46" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -11262,16 +11265,16 @@
         <v>358</v>
       </c>
       <c r="C47" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D47" t="s">
         <v>705</v>
       </c>
       <c r="E47" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -11285,10 +11288,10 @@
         <v>705</v>
       </c>
       <c r="E48" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -11305,7 +11308,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -11322,7 +11325,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -11339,7 +11342,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -11353,7 +11356,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -11367,7 +11370,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -11381,7 +11384,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -11395,7 +11398,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -11409,7 +11412,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -11426,7 +11429,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -11443,7 +11446,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -11460,7 +11463,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -11474,7 +11477,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -11488,7 +11491,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -11502,7 +11505,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -11516,7 +11519,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -11530,7 +11533,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -11544,7 +11547,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -11568,8 +11571,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -11578,7 +11581,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>774</v>
       </c>
@@ -11598,7 +11601,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>780</v>
       </c>
@@ -11612,11 +11615,11 @@
         <v>782</v>
       </c>
       <c r="E2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>784</v>
       </c>
@@ -11627,16 +11630,16 @@
         <v>781</v>
       </c>
       <c r="D3" t="s">
+        <v>811</v>
+      </c>
+      <c r="E3" t="s">
+        <v>799</v>
+      </c>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>785</v>
-      </c>
-      <c r="E3" t="s">
-        <v>783</v>
-      </c>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>786</v>
       </c>
       <c r="B4" s="12">
         <v>46184</v>
@@ -11645,16 +11648,16 @@
         <v>781</v>
       </c>
       <c r="D4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E4" t="s">
         <v>783</v>
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B5" s="12">
         <v>46184</v>
@@ -11663,14 +11666,14 @@
         <v>781</v>
       </c>
       <c r="D5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E5" t="s">
         <v>783</v>
       </c>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>692694</v>
       </c>
@@ -11681,13 +11684,13 @@
         <v>781</v>
       </c>
       <c r="D6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E6" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>708274</v>
       </c>
@@ -11698,13 +11701,13 @@
         <v>781</v>
       </c>
       <c r="D7" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E7" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>691920</v>
       </c>
@@ -11715,13 +11718,13 @@
         <v>781</v>
       </c>
       <c r="D8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E8" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>691923</v>
       </c>
@@ -11732,13 +11735,13 @@
         <v>781</v>
       </c>
       <c r="D9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E9" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>701797</v>
       </c>
@@ -11749,13 +11752,13 @@
         <v>781</v>
       </c>
       <c r="D10" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E10" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>701540</v>
       </c>
@@ -11766,13 +11769,13 @@
         <v>781</v>
       </c>
       <c r="D11" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E11" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>692683</v>
       </c>
@@ -11783,9 +11786,60 @@
         <v>781</v>
       </c>
       <c r="D12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E12" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>701678</v>
+      </c>
+      <c r="B13" s="30">
+        <v>46152</v>
+      </c>
+      <c r="C13" t="s">
+        <v>781</v>
+      </c>
+      <c r="D13" t="s">
+        <v>810</v>
+      </c>
+      <c r="E13" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>701675</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>781</v>
+      </c>
+      <c r="D14" t="s">
+        <v>810</v>
+      </c>
+      <c r="E14" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <v>664339</v>
+      </c>
+      <c r="B15" s="30">
+        <v>46152</v>
+      </c>
+      <c r="C15" t="s">
+        <v>781</v>
+      </c>
+      <c r="D15" t="s">
+        <v>810</v>
+      </c>
+      <c r="E15" t="s">
         <v>783</v>
       </c>
     </row>
@@ -11796,22 +11850,23 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A2:E89"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -11825,7 +11880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -11839,7 +11894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -11853,7 +11908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -11867,7 +11922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -11881,7 +11936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -11895,7 +11950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -11909,7 +11964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>4</v>
       </c>
@@ -11923,7 +11978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>4</v>
       </c>
@@ -11937,7 +11992,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -11951,7 +12006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>4</v>
       </c>
@@ -11965,7 +12020,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>4</v>
       </c>
@@ -11979,7 +12034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>4</v>
       </c>
@@ -11993,7 +12048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>4</v>
       </c>
@@ -12007,7 +12062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>4</v>
       </c>
@@ -12021,7 +12076,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>4</v>
       </c>
@@ -12035,7 +12090,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -12049,7 +12104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="7">
         <v>46092</v>
       </c>
@@ -12063,7 +12118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="7">
         <v>46092</v>
       </c>
@@ -12077,7 +12132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="7">
         <v>46092</v>
       </c>
@@ -12091,7 +12146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="7">
         <v>46092</v>
       </c>
@@ -12105,7 +12160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="7">
         <v>46092</v>
       </c>
@@ -12119,7 +12174,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="7">
         <v>46092</v>
       </c>
@@ -12133,7 +12188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="7">
         <v>46092</v>
       </c>
@@ -12147,7 +12202,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="7">
         <v>46119</v>
       </c>
@@ -12161,7 +12216,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="7">
         <v>46119</v>
       </c>
@@ -12175,7 +12230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7">
         <v>46119</v>
       </c>
@@ -12189,7 +12244,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="7">
         <v>46119</v>
       </c>
@@ -12203,7 +12258,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="7">
         <v>46121</v>
       </c>
@@ -12217,7 +12272,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="7">
         <v>46121</v>
       </c>
@@ -12231,7 +12286,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="7">
         <v>46126</v>
       </c>
@@ -12245,7 +12300,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="7">
         <v>46134</v>
       </c>
@@ -12259,7 +12314,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="7">
         <v>46134</v>
       </c>
@@ -12273,7 +12328,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="7">
         <v>46142</v>
       </c>
@@ -12287,7 +12342,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="7">
         <v>46160</v>
       </c>
@@ -12301,7 +12356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="7">
         <v>46169</v>
       </c>
@@ -12315,7 +12370,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="7">
         <v>46170</v>
       </c>
@@ -12329,7 +12384,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
         <v>46170</v>
       </c>
@@ -12343,7 +12398,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="7">
         <v>46170</v>
       </c>
@@ -12357,7 +12412,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="7">
         <v>46171</v>
       </c>
@@ -12371,7 +12426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="7">
         <v>46171</v>
       </c>
@@ -12385,7 +12440,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="7">
         <v>46171</v>
       </c>
@@ -12399,7 +12454,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="7">
         <v>46171</v>
       </c>
@@ -12413,7 +12468,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="7">
         <v>46171</v>
       </c>
@@ -12427,7 +12482,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="7">
         <v>46175</v>
       </c>
@@ -12441,7 +12496,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="7">
         <v>46175</v>
       </c>
@@ -12455,7 +12510,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="7">
         <v>46175</v>
       </c>
@@ -12469,7 +12524,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="7">
         <v>46175</v>
       </c>
@@ -12483,7 +12538,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="7">
         <v>46175</v>
       </c>
@@ -12497,7 +12552,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="7">
         <v>46175</v>
       </c>
@@ -12511,7 +12566,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
         <v>46178</v>
       </c>
@@ -12525,7 +12580,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="7">
         <v>46178</v>
       </c>
@@ -12539,7 +12594,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="7">
         <v>46178</v>
       </c>
@@ -12553,7 +12608,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="7">
         <v>46178</v>
       </c>
@@ -12567,7 +12622,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="7">
         <v>46178</v>
       </c>
@@ -12581,7 +12636,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="7">
         <v>46184</v>
       </c>
@@ -12595,7 +12650,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="7">
         <v>46188</v>
       </c>
@@ -12609,7 +12664,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="7">
         <v>46189</v>
       </c>
@@ -12623,7 +12678,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="7">
         <v>46189</v>
       </c>
@@ -12637,7 +12692,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="7">
         <v>46211</v>
       </c>
@@ -12651,7 +12706,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" s="7">
         <v>46212</v>
       </c>
@@ -12665,7 +12720,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" s="7">
         <v>46212</v>
       </c>
@@ -12679,7 +12734,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" s="7">
         <v>46212</v>
       </c>
@@ -12693,7 +12748,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B65" s="7">
         <v>46212</v>
       </c>
@@ -12707,7 +12762,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B66" s="7">
         <v>46212</v>
       </c>
@@ -12721,7 +12776,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B67" s="7">
         <v>46212</v>
       </c>
@@ -12735,7 +12790,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B68" s="7">
         <v>46212</v>
       </c>
@@ -12749,7 +12804,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B69" s="7">
         <v>46212</v>
       </c>
@@ -12763,7 +12818,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B70" s="7">
         <v>46212</v>
       </c>
@@ -12777,7 +12832,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B71" s="7">
         <v>46216</v>
       </c>
@@ -12791,7 +12846,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B72" s="7">
         <v>46216</v>
       </c>
@@ -12805,7 +12860,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B73" s="7">
         <v>46216</v>
       </c>
@@ -12819,7 +12874,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B74" s="7">
         <v>46225</v>
       </c>
@@ -12833,7 +12888,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B75" s="7">
         <v>46240</v>
       </c>
@@ -12847,7 +12902,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B76" s="7">
         <v>46240</v>
       </c>
@@ -12861,7 +12916,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B77" s="7">
         <v>46245</v>
       </c>
@@ -12875,7 +12930,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B78" s="7">
         <v>46246</v>
       </c>
@@ -12889,7 +12944,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="16">
         <v>46247</v>
@@ -12904,7 +12959,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B80" s="16">
         <v>46251</v>
       </c>
@@ -12918,7 +12973,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B81" s="16">
         <v>46253</v>
       </c>
@@ -12932,7 +12987,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B82" s="16">
         <v>46253</v>
       </c>
@@ -12946,7 +13001,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" s="16">
         <v>46253</v>
       </c>
@@ -12957,10 +13012,10 @@
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B84" s="16">
         <v>46253</v>
       </c>
@@ -12971,10 +13026,10 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B85" s="16">
         <v>46253</v>
       </c>
@@ -12985,10 +13040,10 @@
         <v>33</v>
       </c>
       <c r="E85" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B86" s="16">
         <v>46253</v>
       </c>
@@ -12999,10 +13054,10 @@
         <v>64</v>
       </c>
       <c r="E86" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" s="16">
         <v>46253</v>
       </c>
@@ -13013,10 +13068,10 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B88" s="16">
         <v>46253</v>
       </c>
@@ -13030,7 +13085,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" s="16">
         <v>46253</v>
       </c>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -13963,7 +13963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E112"/>
+  <dimension ref="A2:E118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="29" min="1" max="1"/>
@@ -16228,6 +16228,126 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="B113" s="16" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>Tarjetas KPI del Resumen unificadas: Operaciones activas va primero; Cláusulas (vencidas / vencen ≤180 días), Productos críticos (retrasados / pausados) y Acuerdos (vencidos / vencen ≤30 días) muestran sus dos valores en una sola tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Productos Críticos / Resultados</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>El popup de adquisición crítica muestra la etapa del proceso: si hay contrato, contratista, monto (moneda original), fecha de firma y fin estimado; si está previsto, fecha esperada de inicio; si está en curso, fecha esperada de firma del contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>Raw Data</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>Se lee el nuevo archivo Contracts and Amendments (contratos registrados en el nuevo módulo del portal) junto con el Raw Data de cada operación; el archivo es opcional</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Raw Data</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>CR-L1032, CR-L1139, CR-L1137, CR-J0002, CR-L1151, CR-L1157</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>Se actualizan los Raw Data de todas las operaciones y se agregan los Contracts and Amendments de 3071_OC-CR, 4864_OC-CR, 4871_OC-CR, 5777_GR-CR y 5823_OC-CR (6061_OC-CR no tiene)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="16" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C117" s="15" t="inlineStr">
+        <is>
+          <t>Productos Críticos / Resultados</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E117" s="15" t="inlineStr">
+        <is>
+          <t>Los contratos pagaderos en varias monedas (una fila por moneda en Contracts and Amendments) muestran la suma de sus montos; p. ej. CR-J0002-P00189: CRC 1 610 690 000 + USD 550 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="16" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Se actualizan README y manual Word: tarjetas del Resumen, archivo Contracts and Amendments, etapa del proceso en el popup de adquisición y operaciones que ya tienen el archivo complementario</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -11971,7 +11971,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A2:E118"/>
+  <dimension ref="A2:E119"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -13620,6 +13620,26 @@
         <v>846</v>
       </c>
     </row>
+    <row r="119">
+      <c r="B119" s="16" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C119" s="15" t="inlineStr">
+        <is>
+          <t>Raw Data</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>Los Raw Data y Contracts and Amendments se movieron a la carpeta clientportal/; index.html ahora los busca ahí. README y manual Word actualizados con la nueva ubicación y la carpeta pmr reports/ (insumos del PMR, el dashboard no la lee)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -11971,7 +11971,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A2:E119"/>
+  <dimension ref="A2:E120"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -13640,6 +13640,26 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" s="16" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>Visor de adquisiciones</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>Propuesta de visor Gantt (visor-adquisiciones.html, página aparte de index.html): una barra por proceso segmentada por fase de hitos del portal del cliente, ejecución del contrato, atrasos y filtros; documentado en README y manual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -14141,7 +14141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E124"/>
+  <dimension ref="A2:E125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col width="3.6640625" customWidth="1" style="30" min="1" max="1"/>
@@ -16646,6 +16646,26 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="B125" s="16" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C125" s="15" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E125" s="15" t="inlineStr">
+        <is>
+          <t>Se actualizan README y manual Word: nuevo skill torre-control-equipo-desde-convergencia (tabla de skills y sección "Barrido del equipo desde Convergencia"), regla de roles fijos en la hoja equipo y descripción de sus filas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
